--- a/witcher_info.xlsx
+++ b/witcher_info.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Magisterka\Magisterka\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{72B0C7F2-DD56-49F3-8EAF-013602F3CFC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F62DAB6C-3E53-4665-9EE6-1269F2AEC197}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="7" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="31" activeTab="36" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="D_NilfgardOficer" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,17 @@
     <sheet name="N_Battle" sheetId="28" r:id="rId28"/>
     <sheet name="N_Ge'els" sheetId="29" r:id="rId29"/>
     <sheet name="N_Sunstone" sheetId="31" r:id="rId30"/>
-    <sheet name="OL_First" sheetId="8" r:id="rId31"/>
+    <sheet name="IM_CrachCraite" sheetId="32" r:id="rId31"/>
+    <sheet name="IM_Dettlaff" sheetId="33" r:id="rId32"/>
+    <sheet name="IM_Dudu" sheetId="39" r:id="rId33"/>
+    <sheet name="IM_Caranthir" sheetId="40" r:id="rId34"/>
+    <sheet name="IM_Radovid" sheetId="41" r:id="rId35"/>
+    <sheet name="IM_Djin" sheetId="34" r:id="rId36"/>
+    <sheet name="IM_Sylvan" sheetId="35" r:id="rId37"/>
+    <sheet name="IM_WaterHag" sheetId="36" r:id="rId38"/>
+    <sheet name="IM_Griffin" sheetId="37" r:id="rId39"/>
+    <sheet name="IM_Ghoul" sheetId="38" r:id="rId40"/>
+    <sheet name="OL_First" sheetId="8" r:id="rId41"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -55,44 +65,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="157">
-  <si>
-    <t>Geralt: Geralt of Rivia. Witcher.
-Nilfgaardian Officer 01: A vatt'ghern - this explains why I did not hear your footsteps. What do you seek here?
-Geralt: Yennefer of Vengerberg. Where was she headed?
-Nilfgaardian Officer 01: That is a military secret.
-Geralt: Haven't thrown me out yet. Haven't called the guards. So go ahead - what's your price?
-Nilfgaardian Officer 01: There is a griffin in the area. Slay it, and then I shall see what I can do.
-Geralt: It's a deal. Some questions before I start. Know where the griffin has its lair?
-Nilfgaardian Officer 01: It kept to the Vulpine Woods at first. I sent a patrol there, five young men. A hunter found them two days on. I only recognized them because they wore our plate.
-Nilfgaardian Officer 01: Since then, the griffin has grown bold. Attacks in villages, fields, on the main road.
-Geralt: Meaning it's abandoned its lair. Gonna have to set a trap.
-Nilfgaardian Officer 01: I judge from your tone this will not be easy. What do you require?
-Geralt: I'll need bait, a specific herb - buckthorn. Scent should lure the griffin from ten miles off.
-Nilfgaardian Officer 01: Buck… buckthorn? I do not know this. But I am not yet fluent in the Common tongue.
-Geralt: Mhm. Probably mastered the basics, though - "hands up," "kill them"…
-Nilfgaardian Officer 01: No. First came idioms. "Don't play with fire," for example.
-Nilfgaardian Officer 01: Go to Tomira, an herbalist. She lives near the crossroads. She will aid you.</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="181">
   <si>
     <t>After rescuing the merchant Bram from the clutches of a rabid royal griffin, the two witches of the Wolf Guild school, Geralt of Rivia and his master Vesemir, were directed to an inn in White Orchard so that there they could inquire about the woman they were looking for, the sorceress Yennefer. So the monster slayers went to the inn where they asked the travelers about Geralt's beloved. There the Witcher Geralt met Professor Aldert Geert, who introduced him to the game of threads, and also listened to local superstitions about the Harbinger of War. However, he received real information about his beloved from a wandering merchant, Gaunter o'Dima, who directed him to a fortress where a Nilfgaard garrison was set up, claiming that a scout there had recently seen the sorceress[1]. Geralt went to the indicated place where he made a deal with Captain Peter Saar Gwynlew. The captain promised to give the witcher information about Yennefer if he would slaughter the enraged royal griffin. He also directed him to the herbalist Tomira and the hunter Myslaw, who were to help him prepare for the hunt. Geralt met Myslaw during his hunt for feral dogs that were threatening people in the area[1].Myslaw gladly accepted the witcher's help and together they took care of the animals. They also found the corpse of Pieter, a stable boy who years ago revealed his relationship with Florian to the heir. The hunter could then tell Geralt his story and explain why he had been banished from the village. After this, he led Geralt to the site of the murder of the Nilfgaard soldiers, where he parted ways with the monster slayer[1].Walking up the hill, the witcher found the destroyed nest of a griffin, in which lay a slain female. He guessed that the individual who was terrorizing the area was a desperate male royal griffin, as well as what the Nilfgaardians had done to its nest in an attempt to get rid of the monster. Geralt then went to the local herbalist Tomira, who had just taken care of the griffin-injured Lena. The monster slayer learned from the herbalist where he would find the sagebrush he needed to make a trap for the monster. After gathering information about the beast and the necessary ingredients, the witcher returned to Vesemir and together they prepared the ambush. The griffin sensed the jackal and arrived on the scene after just a moment. The two of them dealt with the monster, after which Geralt carried its head to the Nilfgaard captain as proof that he had fulfilled his part of the bargain. Peter Saar Gwynlew gave the witcher information about Yennefer, and the witcher, furious that he had wasted so much time in the village, returned to give a new lead to Vesemir[1]. The Witchers met again at the inn, but there a brawl ensued in which one of the women accused the innkeeper Elza of collaborating with Nilfgaard. Geralt and Vesemir stepped forward to defend the attacked innkeeper, to which a bunch of drunken peasants reacted with aggression. Faced with the threat, the witches were thus forced to draw their steel swords. After a bloody showdown with the peasants, the witches were chased out of the inn by Elza, in whose defense they stood. So the Witchers left White Orchard[1].</t>
-  </si>
-  <si>
-    <t>Dialogue between Geralt of Rivia and a Nilfgaardian officer. Geralt is seeking information about Yennefer of Vengerberg, 
-  while the officer offers to help in exchange for slaying a griffin that has been terrorizing the area. The officer provides details about the griffin's lair and informs Geralt about dead soldiers. 
-  Geralt knows he needs to set a trap for the griffin and requests buckthorn as bait. The officer suggests visiting Tomira, an herbalist, for assistance in obtaining the herb.</t>
-  </si>
-  <si>
-    <t>Geralt: I'm looking for someone. A sorceress. Yennefer of Vengerberg. Have you seen her?
-Nilfgaardian Officer: You're not the first to ask. She passed through. Headed north in haste, escorted by a rider from our intelligence corps. But information has a price.
-Geralt: I don’t barter in coin.
-Nilfgaardian Officer: Good. I need something else. A griffin has made its nest in the hills beyond the forest. It’s killing our patrols, tearing through supply lines. Slay it, and I’ll give you what you want.
-Geralt: Griffin nests don’t just appear. Something drove it here.
-Nilfgaardian Officer: No doubt. Locals say it nested in the ruins by the old watchtower. We’ve found soldiers... or what was left of them. Wings severed, entrails strung from trees. It’s hungry, and it’s angry.
-Geralt: I’ll need to lay a trap. Bait it out. Buckthorn ought to do the trick.
-Nilfgaardian Officer: Then speak to Tomira, the herbalist in the village. She knows the area—and the plants. Help us, witcher, and I’ll ensure your path to Yennefer is cleared.
-Geralt: Fine. I’ll handle your griffin. But when it’s done, I expect truth, not riddles.
-Nilfgaardian Officer: You’ll get what you came for. On my honor.</t>
   </si>
   <si>
     <t>Participants</t>
@@ -354,9 +329,6 @@
 If you chose the witcher's way (either by not trusting Cerys or handing the baby over to the jarl), go talk to Udalryk to tell him about what's been going on with the hym and that you need him to visit his old family home to get rid of it. Hjort will back you up and give you the torches needed for the fight or, if you handed the baby over, send you to the shed to get them. When ready, head out and place the 4 torches and head just outside to talk to Udalryk to let him know it's ready. You can then advise him or not on what's going to happen before heading back in to light the torches.
 During the ensuing fight, you'll need to also use Axii from time to time on Udalryk to calm him down, and eventually the hym will retreat to the cellar. Head down to finish the job and once dead (750 XP earned based on the Story and Swords! difficulty level) go talk with Udalryk to let him know it's finally over.
 Whichever method you chose, Udalryk is finally free from the hym's torment. Cerys then states she'll remain for a little while to make sure of the jarl's recovery before finishing the quest.</t>
-  </si>
-  <si>
-    <t>Dialogue between Cerys and Udalryk, after Cerys plan. She try to convice him that she would never harm his child and explains plan.</t>
   </si>
   <si>
     <t>Write a scene (only dialogues) it's description:</t>
@@ -744,12 +716,6 @@
     <t>Message from Fritz to Wallter and Lussi, about problem with buesiness and his idea of three key chest for their treasure.</t>
   </si>
   <si>
-    <t>To Wallter and Lussi:
-We've got a problem with the business—trust issues are growing, and we need a way to secure our earnings. I suggest we store the treasure in a chest locked with three keys. Each of us will hold one key, so the chest can only be opened when all three are present. This way, no one can take from it alone, and our profits stay safe.
-Let me know what you think.
-— Fritz</t>
-  </si>
-  <si>
     <t>Widower, 60 years of age, of medium height, above-average intellect, possessing a fortune in both species and real estate, seeks old maid or childless widow of a similar age or somewhat older, preferably from a landed family. Those interested are requested to send a missive with a (faithful!) engraving of their likeness included, to Poste Restante Gildorf, c/o "Romantic."
 P.S. No response will be given to letters without a full name and valid return address.
 P.P.S. Women of the elder races, halflings in particular, need not inquire.</t>
@@ -1101,9 +1067,6 @@
   </si>
   <si>
     <t>On Hindarsfjall Geralt and Yen learned that Ciri had returned to the Isles. She'd rejoined her friend, the masked mage. They had boarded a boat and sailed off in an unknown direction. The boat had returned, one passenger on board – a creature as mindless as it was hideous.</t>
-  </si>
-  <si>
-    <t>Geralt and Yennfer finds out that Ciri return to Isles and meet masked mage. They sailed to unknown direction. Their boat return with a mindless creature inside.</t>
   </si>
   <si>
     <t>The Mysterious elf and an unconcious Ciri appear on Skellige, with Skjall being witness to the event. The Mysterious elf will ask for his help and then tell Ciri where they will meet next before he departs. Ciri will now awake and start talking with Skjall. If Ciri asks how long was she out, the conversation can take a turn where Ciri asks Skjall if he stripped her, which he admits doing but declines being the one to rub blubber on her breasts stating that it was his mother and sister who did that. After asking for help with standing up Astrid will join in and ask Ciri to join her in the sauna. Ciri will prefer to leave as soon as possible, however Skjall will tell her she will need a horse to reach Drowned Dead Rock so he will get one ready while she accepts the offer.
@@ -1163,9 +1126,6 @@
     <t>Ge'els had been a loyal subject of the Alder Folk's previous king. When he learned Eredin was a regicide, he agreed to help defeat the usurper.</t>
   </si>
   <si>
-    <t>Convincing Ge'els to betray Eredin because he is regicide.</t>
-  </si>
-  <si>
     <t>To start the quest, talk to Avallac'h about what you did on Bald Mountain. He will inform Geralt that his victory over Imlerith made him believe that they may have a chance at victory after all. He has a plan about one of Eredin's two remaining generals, Ge'els. Eredin had poisoned their former King Auberon Muircetach, to whom Ge'els was loyal and therefore could be convinced to withdraw his support. But of course, you need to find him first, by travelling with Avallac'h to the Aen Elle's capital Tir ná Lia.
 After everything is explained, you'll have the option to go immediately or meet later, near the location of a portal to another world. It happens to be in the basement of the house where you previously met Sarah and Corinne Tilly. Once there, destroy the wall if you haven't previously and approach the portal.
 After entering the portal you will appear in a desert world. Follow Avallac'h to your destination and on the way he will explain that you're walking on a the bottom of a former ocean, which used to be a live being itself. There are also a few tree stumps that you can loot on the way, not detectable using Witcher Senses. Eventually you reach next portal, but you must wait for it to open and you've awakened Sandcrabs that you now have to kill. They will spawn infinitely, but the portal will open after the first wave, so jump in when it does and you will move to the next world.
@@ -1246,23 +1206,6 @@
     <t xml:space="preserve">Write book page about: </t>
   </si>
   <si>
-    <t>Elder races</t>
-  </si>
-  <si>
-    <t>Chapter VII: The Elder Races of the Continent
-The Continent, a vast and unforgiving land, is home not only to humans but to a multitude of other races collectively known as the Elder Races. These ancient peoples existed long before humans crossed the seas, shaping the world through their cultures, magic, and craftsmanship. Among them, four races stand out as the most prominent: Elves, Dwarves, Gnomes, and Halflings.
-Elves:
-Graceful and immortal, elves were the first to establish great civilizations on the Continent. Their cities, woven into the natural world, boast elegant spires and seamless integration with forests and mountains. Skilled in both magic and archery, elves view time differently from humans, their lives unfolding slowly across centuries. Once the dominant race, they are now reduced to scattered enclaves and wandering bands, driven to the margins by human expansion and brutal wars. Despite their decline, elven pride endures, as does their love of music, poetry, and lore.
-Dwarves:
-Short, stout, and immensely resilient, dwarves have long been masters of the forge and the mine. Their strongholds, carved into mountain hearts, are feats of both engineering and artistry. Renowned for their craft, dwarven weapons and armor are sought after across the known world. Practical and blunt, dwarves value loyalty and brotherhood, often forming tight-knit clans. Though once hostile to human encroachment, many now coexist, especially in cities like Novigrad and Oxenfurt, where dwarven blacksmiths and warriors are common sights.
-Gnomes:
-The oldest of the Elder Races, gnomes are diminutive but fiercely intelligent. Their knack for invention rivals even that of dwarves, and they are often credited with teaching humans mining and metallurgy. Preferring seclusion, gnomes live in small, well-hidden communities, mostly in the Mahakam Mountains. While not as openly involved in political struggles, their craftsmanship and knowledge continue to influence the world. Gnomes rarely engage in warfare, yet their traps and mechanical devices are famed for their precision and deadly efficiency.
-Halflings:
-Friendly and unassuming, halflings are the most integrated of the Elder Races within human society. Typically found in peaceful villages or bustling marketplaces, they are skilled farmers, cooks, and traders. Halflings prefer a simple, comfortable life, far from war and conflict. Known for their hospitality and love of good food, they are sometimes overlooked as mere peasants. However, their quick wit and uncanny ability to blend in make them adept at surviving even in hostile regions.
-A Legacy of Struggle:
-The Elder Races have endured countless hardships since the arrival of humans. Their numbers dwindle, and their ancient customs fade. Yet, they persist, holding onto their traditions with a fierce determination. While some, like the elves, choose rebellion, others, like the dwarves and halflings, adapt and coexist. Together, they form a tapestry of cultures often at odds with one another, yet bound by their shared history as the first children of the Continent.</t>
-  </si>
-  <si>
     <t>Cretificate that allows to fight on Junior's arena as Zdenek</t>
   </si>
   <si>
@@ -1344,44 +1287,267 @@
     <t>Ah, Skellige—land of storms and stubborn druids! A mighty magical blast rocked the isles, and Yennefer was convinced it had Ciri’s name written all over it. Geralt joined her, naturally, but the druids weren’t exactly rolling out the welcome wagon. Stubborn as ever, Yennefer decided to cut through the red tape by appealing to a jarl for permission. After all, when magic’s afoot, diplomacy often needs a touch of force!</t>
   </si>
   <si>
-    <t>Ah, Skellige—where mysteries wash ashore like shipwrecked dreams! Geralt and Yennefer uncovered that Ciri had indeed returned to the isles, meeting with a masked mage of all things. The pair set sail to follow her trail, but fate’s winds had other plans. Days later, their boat drifted back to port—empty, save for a mindless wretch babbling incoherently. A chilling clue, yet another twist in the ever-elusive chase.</t>
-  </si>
-  <si>
     <t>Ah, what a reunion that was! Geralt finally found Ciri, and together they whisked away to Kaer Morhen, that old bastion of witcher lore. But peace was short-lived—the Wild Hunt came crashing down like a winter storm. The battle was fierce, blades flashing and magic crackling, but against all odds, the defenders stood firm. Kaer Morhen held its ground, and the Wild Hunt slunk away, licking its wounds.</t>
   </si>
   <si>
-    <t>Now that’s a tale of silver tongues and sharp wits! Geralt, ever the master of persuasion, convinced Ge’els that Eredin—his own king—was a cold-blooded regicide. The revelation hit like a thunderclap, shaking Ge’els’ loyalty to its core. Betrayal, after all, cuts deepest when wielded by one’s own kin. And just like that, another piece of Eredin’s power crumbled to dust.</t>
-  </si>
-  <si>
     <t>Ah, the Naglfar—Eredin’s dreaded ghost ship, cutting through worlds like a blade through silk! That wily elf Ge’els tipped Geralt off, suggesting that the key to stopping the Wild Hunt lay in the legendary Sunstone. With it, they could summon Eredin from his spectral voyage and force a final clash. Of course, finding an ancient elven artifact isn’t exactly a stroll through the woods. But when has Geralt ever shied away from a challenge?</t>
   </si>
   <si>
-    <t>Geralt and Regis talk for the first time from Styga Castle situation.</t>
-  </si>
-  <si>
-    <t>Geralt: "Didn't think you'd pick Toussaint of all places."
-Regis: "A place of beauty and serenity... thought I could use both. Besides, the vineyards remind me of home."
-Geralt: "Can't say I blame you. A bit odd seeing you here, though... after everything."
-Regis: "I needed time. To reflect. To grieve. To understand what... what I became at Stygga."
-Geralt: "You were yourself, Regis. Doing what needed to be done. Dettlaff... he was already lost."
-Regis: "Lost, yes. But not beyond saving. I believed... no, I wanted to believe there was still a chance. That I could reach him."
-Geralt: "Sometimes, you can't save those who don't want saving."
-Regis: "I told myself that a thousand times. Doesn’t make it any easier. I wanted to be the one who understood him... guided him. Instead, I led him to his death."
-Geralt: "Dettlaff chose his path. You did what a friend does—tried to help. But when blood's spilled... you know as well as I do, there's no going back."
-Regis: "A vampire who failed to control his instincts... and a friend who failed to stop him. A rather tragic tale, don’t you think?"
-Geralt: "Toussaint’s full of tragic tales. People around here would make a ballad out of it. 'The Lost Friend and the Last Dance.' Might even sell a few copies."
-Regis: "You jest... but I suppose you're right. Pain makes for good stories."
-Geralt: "Or good company. Either way, you’re still here. Means you’re not done just yet."
-Regis: "Perhaps. If anything, I owe it to Dettlaff... to make something of this existence."
-Geralt: "Sounds like a plan. Just... keep it quiet. Last thing I need is another riot on your account."
-Regis: "I’ll do my best. I promise."</t>
+    <t>Skellige sagas brim with praise for war chiefs and warrior-braves of ages past, yet the saga of Crach, jarl of the Clan an Craite and lord of Kaer Trolde, will outshine them all. It will sing of his strength, his courage, his wisdom, his generosity, his loyalty to friends and his relentless pursuit of his foes.
+There will be few exaggerations in such a tale, for Crach, the mightiest of Skellige's jarls, truly did possess all the traits of a hero. He aroused terror in his enemies – in fact, Nilfgaardian mother would use his name to frighten their children into obedience, and all in that empire spoke in hushed tones of the infamous Tirth ys Muire, the Wild Boar of the Sea, who devastated coastal provinces during frequent and terrible raids.
+Geralt had known Crach for long, since a time when as a young man the jarl had sought the hand of young Pavetta, Ciri's mother.</t>
+  </si>
+  <si>
+    <t>Crach an Craite, also known as "Tirth ys Muire" ("Sea Boar") and the "Wild Boar of the Sea", was a nephew of King Bran of Skellige and was mentored by Eist Tuirseach, king of Cintra. He was described as a broad shouldered youth with a mop of red hair and is known for sometimes showing quite a temper. He wasn known for his fiery temperament and healthy appetite.
+In his early years he was a contender for the hand of Pavetta, Princess of Cintra, however, it never came to anything. After the death of his uncle Eist Tuirseach, who had inherited the throne of King Bran, Crach became the Jarl and thus, the ruler of the Skellige Islands.
+He also had a brief affair with Yennefer and remained fond of her afterwards, which he demonstrated by helping her in her search for Vilgefortz.</t>
+  </si>
+  <si>
+    <t>It was horrifying to watch... that gentleman suddenly turned into a ghastly beast, with claws, and... tore those men to shreds with the precision of a master butcher…
+– a witness to Dettlaff's attacks
+Dettlaff is a higher vampire and one of the most terrifying creatures the world has ever known. Some vampires of his sort live among men easily and inconspicuously, sometimes even gaining the respect and admiration of their community. Yet even the most civilized vampire can be incredibly dangerous if provoked, and Dettlaff... Dettlaff was far from civilized.
+When in his two-legged form, Dettlaff strikes in surprising and unique ways, so one must be extremely alert and attentive. His razor-sharp claws, wielded with great strength and precision, are his chief weapons, yet he can also wield weapons of human devising with extraordinary skill.</t>
+  </si>
+  <si>
+    <t>The pitcher emitted a puff of glowing red smoke. The smoke pulsated, then gathered up into an irregular sphere floating in front of the poet's head...
+–The First Longing, a Tale Fantastic in All Ways.
+A djinn is a powerful air spirit, a condensation of the power of that element endowed with consciousness and character - the latter usually nasty. According to legend, djinns can grant even the most far-fetched wishes, though they do so very begrudgingly.
+Unusually powerful mages can capture and tame these beings. The mage can then draw on its energy, using it to cast spells without having to call on Power from traditional sources. Only a sparse handful have managed this feat, however, for djinns fight to avoid such a fate with stubborn determination. To imprison a djinn and bend it to one's will, one must first weaken it - and that is no easy feat.
+Fighting a djinn is extraordinarily difficult. They can fling off spells in an instant that the most accomplished human mages could never cast with years of preparation. What's more, by manipulating the element of air they can summon powerful storms, hurricanes and gales. Luckily, as magic beings they are vulnerable to silver - yet steel will do them no harm.</t>
+  </si>
+  <si>
+    <t>Sylvans are cruel, greedy and treacherous. Still, I prefer them to dh'oine.
+— Yaevinn, legendary Scoia'tael commander
+Sylvans and Yakshas, a kindred species, are extremely rare woodland creatures whose appearance combines traits of goats and rotund men. These beings usually pose little danger, for they limit their contact with humans to playing harmless (though often bothersome) tricks and eating crops from their fields.</t>
+  </si>
+  <si>
+    <t>Folk say water hags are drowner's wives. If that be true, 'tain't no wonder why they're such ornery bitches.
+— Shemhel of Dregsdon
+Some tales mention water hags and swamp bints masquerading as lost old women to lure travelers back to the rickety shacks they build in the wetlands. In truth, only a blind man, or a sighted man blinded with drink, could mistake the rank sludge and rotting carrion of a water hag's den for a cozy cottage, and the hideous hag herself for an innocent grandmother. Their wrinkled, wart-covered bodies stand nearly two yards tall, with skin the color of a long-dead cadaver and stinking of much and fish. Bony growths two spans long stick out from their backs, with hair like a tangle of seaweed and claws that would make a werewolf proud completing the picture.</t>
+  </si>
+  <si>
+    <t>Aye, half-eagle, half tomcat, just like on the lord's crest. 'Cept this 'un was carryin' me dead cow 'stead of a scepter.
+— Griffin attack witness, name unknown
+Griffins were once only found high in the mountains, where they would hunt marmots and wild goats. When humans encroached on their lands, however, griffins soon discovered a new source of much more plentiful and easier-caught prey: cows, sheep and shepherds. Though still wary of main roads and towns (where fold with the means to hire a witcher are like to dwell), these half-eagle, half-wildcat creatures have gone from rarities to oft-encountered pests known throughout the Northern Realms. Especially hated are the subspecies known as royal griffins and archgriffins.</t>
+  </si>
+  <si>
+    <t>The griffin looks like a combination of a ferocious cat and a giant bird. It usually inhabits primeval highlands and builds its nests on unreachable mountain summits. The griffin preys on large mammals and, being a highly territorial creature, fiercely defends its hunting grounds. When the first colonists appeared and trade routes expanded, griffins were known to attack settlers and merchants in defense of their territory. Griffins are tough opponents and their strength should not be underestimated. Obstinate and aggressive, they make deadly use of their ability to fly during combat, swooping down on their enemies, knocking them to the ground and ripping them to shreds with their claws and beak.</t>
+  </si>
+  <si>
+    <t>Water hags are monsters introduced in The Witcher 3: Wild Hunt. As their name suggests, they are found in swampy areas, near boat landings and tend to guard treasures. They are often accompanied by drowners.</t>
+  </si>
+  <si>
+    <t>The creature was about half a rod tall with bulging eyes and a goat's horns and beard. The mouth, a soft, busy slit, also brought a chewing goat to mind. Its nether regions were covered with long, thick, dark-red hair right down to the cleft hooves. The devil had a long tail ending in a brush-like tassel which wagged energetically.</t>
+  </si>
+  <si>
+    <t>Going back to genies, there are four sorts, just as there are four Planes. Djinns are air creatures; marides are associated with the principle of water; afreet are Fire genies and d’ao, the genies of Earth—
+[...]
+Word has it old Monck had a way of forcing a djinn to serve him. There were rumours that he had more than one. He was said to keep them in bottles and make use of them when need arose. Three wishes from each genie, then it's free and escapes into its own dimension.</t>
+  </si>
+  <si>
+    <t>Dettlaff van der Eretein is a higher vampire who rescued Regis after the latter had seemingly been killed by Vilgefortz during the assault on Stygga castle. Geralt and his companions had — not surprisingly — assumed being reduced to a puddle of plasma was a fatal condition, but Dettlaff was able to help Regis regenerate fully. For this, the former barber-surgeon would be forever grateful.</t>
+  </si>
+  <si>
+    <t>Ghouls creep and crawl at night
+Eating everything in sight
+In a snap they'd eat you, too
+Chop you up for a ghoulish stew!
+— Children's rhyme
+Ghouls and graveirs are hard to describe. In part, they resemble humans – yet on the whole, they are the utter negation of all that is human. Though they have arms and legs like men, they walk on all fours like dogs or badgers. Though they have eerily familiar faces, one searches them in vain for any sign of sentiment, reason or even a spark of consciousness. They are driven by one thing and one thing only: an insatiable craving for human flesh.</t>
+  </si>
+  <si>
+    <t>After the Great War, necrophages generally grew bolder and multiplied in the Northern Kingdoms. Ghouls are the most common corpse-eaters and usually roam around in packs. For a ghoul, a living human is raw material that must be processed before it can become a meal. Shredded to pieces with fangs and claws, the human corpse should then be left to age.</t>
+  </si>
+  <si>
+    <t>You see, we first unwittingly talked to him when he was in Novigrad impersonating another friend of mine, a halfling merchant named Dainty Biberveldt. Dudu had assumed Dainty's form to use the merchant's network of contacts for some business endeavors of his own.
+Dainty was infuriated at first at his inability to locate the impostor who had inserted himself into his dealings, but when Dudu's investments began generating sizable returns, the halfling changed his tune. He took the doppler on as a partner, introducing him to everyone as his cousin, Dudu Biberveldt.</t>
+  </si>
+  <si>
+    <t>Tellico Lunngrevink Letorte, or Penstock for short, or Dudu for friends - a doppler formerly living in Novigrad under the guise of Daintie Biberveldt, initially against his will. However, through a series of brilliant business moves, Dudu gained the sympathy of this lowlander, and the latter allowed him to use his persona and act as his factotum in the city. From then on, Dudu was considered Dainty's cousin. In Wild Game, he lost his property and his right eye through Skurwiel Junior, and after Junior's death he impersonated him. 2 weeks after Skurwiel's death, he proclaimed that he had converted to Eternal Fire, sold his illegal business and is engaged in deep-sea trading.
+He is short. He is bald and has a prominent nose and protruding ears. He is missing his right eye, the place of which is occupied by a wide scar also visible after the transformation.
+Dudu is a positive character perfectly capable of turning a fortune. He has a fondness for the arts, and because of his abilities he often performed on stage, replacing indisposed artists. He is characterized by a good-naturedness that he cannot get rid of even after his transformation.
+Dudu wears a brown and green vest.</t>
+  </si>
+  <si>
+    <t>This Aen Elle elf was one of Eredin's advisors and also, on account of his extraordinary abilities, an important officer of the Wild Hunt. Calling on arcane magic Caranthir would guide the Riders of the Hunt along mystic pathways through time and space in order to reach other worlds.
+He was also a master of more immediate forms of transport, such as the teleportation he made ample use of during the attack on Kaer Morhen.
+Yet even with his tricks and spells Caranthir still died during the final battle against the Wild Hunt, his body swallowed up by the cold waters of the ocean.</t>
+  </si>
+  <si>
+    <t>Caranthir was the product of Avallac'h's attempts to breed a gifted child from elven couples who possessed great ability in manipulating time and space. He was an incredibly talented student, but later turned criminal. His birth was meticulously planned by Avallac'ha, who had been pairing Aen Saevherne for years to obtain an elf who could match the descendants of Larry Dorren in talent. When Caranthir was born he was placed under the continued care of Crevan, who prepared him for the role he would play in the history of Aen Elle. However, the Avallac'ha alum decided that he would put his skills to better use serving in the ranks of Dearg Ruadhri, and thus became Naglfaar's navigator and Eredin's most trusted officer. Caranhtir was distinguished not only by his immense talent, but also by his character. As enigmatic and reticent as his former mentor, he was distinguished by honor and rare loyalty.</t>
+  </si>
+  <si>
+    <t>It did not take long for King Radovid of Redania to prove himself a hard and ruthless ruler, one fully deserving to be styled "the Stern." His father, King Vizimir, was murdered when Radovid was quite young, and his mother, Hedwig of Malleore, and a Regency Council ruled in his stead.
+Young Radovid soon seized power in his own right, however, and wrought vengeance on those who had treated him with disrespect. He took to forcing all his potential political opponents to swear allegiance – or face death.
+He waged war not only against Nilfgaard, but also against mages, whom he saw as the root of all evil. Radovid also made every effort to gain control over the Free City of Novigrad, whose fleet and treasury could tip the scales of the ongoing conflict towards Radovid's victory.</t>
+  </si>
+  <si>
+    <t>Radovid V the Harsh - King of Redania, son of Vizimir and Hedwig of Malleore. Born in 1255, he took over the reign after the Regency Council.
+At the time of the events of the Saga, he was 13 years old (Lady of the Lake). The youngest brother of Dalka and Milena. During the events of The Witcher 2, he took the reigns of his kingdom.
+Characteristics
+He is a young ruler whose burden of the crown has aged considerably. He is characterized by a lack of patience and great ambition. He can be very brutal, and has a special hatred for wizards, most notably his father's former advisor Philippa Eilhart. He gained a powerful ally in the form of the Order of the Burning Rose, his inquisitors sought out and exterminated any signs of magic.
+Unfoundedly, he is considered by many to be of unsound mind. However, this did not prevent him from successfully fighting the Nilfgard Empire. In doing so, his ability to anticipate the enemy's movements and choose the right strategy was invaluable.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Write text to game Witcher 3: Wild Hunt. Your guideline:
+Creators: Geralt of Rivia, Regis 
+Type of text: Dialogue (only words without body expresion) 
+Length: max 200 words 
+Content:
+- List of  facts that need to be contained: [“Geralt and Regis meet in Tousaint first time from Styga Castle event”, “They talk about how Regis is even alive”, "Geralt is sorry for what happend"] 
+- Participants: Geralt of Rivia, Regis </t>
+  </si>
+  <si>
+    <t>Geralt: Regis...?
+Regis: Geralt. A pleasant surprise.
+Geralt: Thought you were dead. Stygga Castle... Vilgefortz...
+Regis: Understandable. It did look rather final.
+Geralt: Final? Regis, you were... in pieces.
+Regis: Yes. Quite a few, actually. It took... time to recover. A long, painful process.
+Geralt: How? I’ve never heard of a vampire coming back from... that.
+Regis: Higher vampires are a peculiar lot. Death, as you understand it, is more of an inconvenience for us. Regeneration is possible, though slow.
+Geralt: Thought I’d never see you again. Thought... I failed you.
+Regis: Failed? Nonsense. You did what you could. Vilgefortz was... formidable.
+Geralt: Still... I should’ve done more.
+Regis: You always did blame yourself too harshly. I hold no grudge. The past is the past.
+Geralt: Can’t help it. Stygga’s left scars.
+Regis: On us both. But we’re here, Geralt. Alive. Or as close to it as we get.
+Geralt: Yeah... Good to see you, Regis.
+Regis: Likewise, old friend.</t>
+  </si>
+  <si>
+    <t>Letter from Fritz to Wallter and Lussi
+Wallter, Lussi,
+I hope this letter finds you both well. We’ve got ourselves a bit of a problem with the business. The guards in Novigrad are becoming nosy, and there’s talk that someone might have spilled a few too many details about our little operation. We need to be careful.
+For now, I’ve moved the loot to my place. Safer that way. Don’t get the wrong idea—I’m not trying to trick you. We’ve worked too hard to let greed ruin it. I’ve come up with a plan to keep it secure: a chest with three locks, each with a different key. One for me, one for you, Wallter, and one for you, Lussi. This way, no one can get to the stash without all of us agreeing. Fair and square.
+Let me know what you think. We’ll meet in the usual spot to sort it out. Until then, keep your heads down and your mouths shut.
+Fritz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title: A Treatise on the Elder Races
+Author: Master Elgar of Oxenfurt
+The Continent, as we know it, is a tapestry woven from diverse races and cultures, some ancient, others more recent. Among these, the so-called "Elder Races" hold a position of particular significance, having shaped the world long before humans claimed dominion.
+4. The Elves
+Of all Elder Races, the Aen Seidhe, commonly referred to as elves, are perhaps the most renowned. Graceful, long-lived, and deeply attuned to nature, elves once reigned over vast territories. Their architectural marvels, now often overgrown ruins, hint at a golden age before human expansion. The Elves are adept with both the bow and the magical arts, blending martial prowess with ethereal finesse. Despite their dwindling numbers, they maintain pride in their heritage, though many now live as outcasts or rebels in human lands.
+5. The Dwarves
+In contrast to the elves’ elegance, the dwarves of Mahakam embody resilience and craftsmanship. Stout, hardy, and industrious, they carve their mountain halls with a precision unmatched by any human mason. Though distrustful of sorcery, dwarves have mastered metallurgy, their steel being the envy of many. Unlike elves, dwarves have managed to coexist with humans to some degree, often forming merchant guilds or taking up arms as mercenaries.
+6. The Gnomes
+Predating even the dwarves, gnomes are the true ancients of the Continent. Smaller in stature but equal in ingenuity, they are master artisans and inventors. Rarely seen in cities, they prefer secluded valleys where they pursue their crafts. Though less influential in politics, their creations — from fine jewelry to intricate mechanisms — remain highly coveted.
+7. The Halflings
+A more recent addition to the Elder Races, halflings are often mistaken for gnomes due to their small stature. Yet, they differ greatly in temperament and lifestyle. Halflings value comfort, agriculture, and communal living. Their resilient spirit and uncanny knack for gardening have made them beloved, albeit underestimated, members of many human settlements.
+8. Conclusion
+The Elder Races once dominated the Continent, their cultures thriving in harmony with the land. However, the arrival and expansion of humanity shifted the balance irrevocably. Today, remnants of their grandeur persist, standing as silent witnesses to an era where magic, craftsmanship, and tradition held sway over the world. Understanding these races is not merely a matter of history but a key to comprehending the soul of the Continent itself.
+</t>
+  </si>
+  <si>
+    <t>Write text to game Witcher 3: Wild Hunt. Your guideline:
+Creators: Book Author
+Type of text: Book Page
+Length: max 400 words 
+Content:
+-  Thmetic: Elder Races
+-  Tone: Scientific text</t>
+  </si>
+  <si>
+    <t>In their relentless pursuit of Ciri, Geralt and Yennefer uncover troubling news: Ciri has returned to the Isles, accompanied by a masked mage. The two set sail, vanishing into the unknown. Days later, their boat drifts ashore—empty, save for a mindless creature babbling incoherently. A dark shiver runs through the Witcher and sorceress alike, for this eerie passenger hints at a fate worse than death.</t>
+  </si>
+  <si>
+    <t>Write text to game Witcher 3: Wild Hunt. Your guideline:
+Creators: Dandelion
+Type of text: Narration
+Length: max 70 words
+ Content:
+-    List of facts that need to be contained: [“Geralt and Yennfer finds out that Ciri return to Isles and meet masked mage.", "Ciri and mage sailed to unknown direction", "Their boat return with a mindless creature inside."]
+ -    Participants: Geralt, Yennefer, Ciri, masked mage</t>
+  </si>
+  <si>
+    <t>Ge'els, noble and proud, learns the bitter truth—Eredin, the supposed savior, is a regicide. Struck by the betrayal, Ge'els swears to aid Geralt, vowing to stand against the tyrant who stained their realm with blood.</t>
+  </si>
+  <si>
+    <t>Write text to game Witcher 3: Wild Hunt. Your guideline:
+Creators: Dandelion
+Type of text: Narration
+Length: max 40 words 
+ Content:
+-    List of facts that need to be contained: [“Convincing Ge'els to betray Eredin because he is regicide.", "Ge'els agrees"] 
+ -    Participants: Ge'el</t>
+  </si>
+  <si>
+    <t>Crach an Craite, Jarl of the powerful Clan an Craite, stands as one of the most respected and influential leaders on the Skellige Isles. Renowned for his unyielding spirit and unwavering loyalty, he commands not just his clan but garners the respect of rival jarls as well. Known for his fierce sense of honor and battle prowess, Crach is also a trusted ally of Geralt of Rivia. Their bond, forged through shared trials and mutual respect, traces back to Crach’s steadfast support during Geralt’s previous visits to Skellige. Though rough around the edges, Crach’s heart beats for his people, his family, and the isles he holds dear. A loyal friend but a fearsome enemy, the Jarl’s name is synonymous with Skellige’s indomitable spirit.</t>
+  </si>
+  <si>
+    <t>Write text to game Witcher 3: Wild Hunt. Your guideline:
+Creators: Dandelion
+Type of text: Glossary Note
+Length: max 150 words 
+ Content:
+-    List of facts that need to be contained: [“Crach character", "Crach position at Skellige", "Crach relation with Geralt"] 
+ -    Thematic: Crach an Craite wihout game events</t>
+  </si>
+  <si>
+    <t>Sylvans—tricksters, pranksters, and notorious gluttons—are rare creatures often mistaken for demons. Though not inherently evil, their fondness for mischief can lead to chaos, especially when they meddle in human affairs. As one old Skellige saying goes: 'A Sylvan’s jest leaves your barn empty and your head aching.' Best to treat them with caution—or better yet, a hefty offering of grain.</t>
+  </si>
+  <si>
+    <t>Write text to game Witcher 3: Wild Hunt. Your guideline:
+Creators: Dandelion
+Type of text: Bestiary Note
+Length: max 80 words 
+ Content:
+-    List of facts that need to be contained: ["Quote about Sylvan"] 
+-    Thematic: Sylvan</t>
+  </si>
+  <si>
+    <t>Geralt: Geralt of Rivia. Witcher.
+Peter Saar Gwynleve: A vatt'ghern - this explains why I did not hear your footsteps. What do you seek here?
+Geralt: Yennefer of Vengerberg. Where was she headed?
+Peter Saar Gwynleve: That is a military secret.
+Geralt: Haven't thrown me out yet. Haven't called the guards. So go ahead - what's your price?
+Peter Saar Gwynleve: There is a griffin in the area. Slay it, and then I shall see what I can do.
+Geralt: It's a deal. Some questions before I start. Know where the griffin has its lair?
+Peter Saar Gwynleve: It kept to the Vulpine Woods at first. I sent a patrol there, five young men. A hunter found them two days on. I only recognized them because they wore our plate.
+Peter Saar Gwynleve: Since then, the griffin has grown bold. Attacks in villages, fields, on the main road.
+Geralt: Meaning it's abandoned its lair. Gonna have to set a trap.
+Peter Saar Gwynleve: I judge from your tone this will not be easy. What do you require?
+Geralt: I'll need bait, a specific herb - buckthorn. Scent should lure the griffin from ten miles off.
+Peter Saar Gwynleve: Buck… buckthorn? I do not know this. But I am not yet fluent in the Common tongue.
+Geralt: Mhm. Probably mastered the basics, though - "hands up," "kill them"…
+Peter Saar Gwynleve: No. First came idioms. "Don't play with fire," for example.
+Peter Saar Gwynleve: Go to Tomira, an herbalist. She lives near the crossroads. She will aid you.</t>
+  </si>
+  <si>
+    <t>Geralt: "I'm looking for a sorceress—Yennefer of Vengerberg. Passed through here recently. Heard anything?"
+Peter Saar Gwynleve: "Yennefer... yes, I've heard the name. Came through just days past. Trouble follows her like a shadow. But if you’re asking, I assume you’ve got business with her?"
+Geralt: "I do. Where’d she go?" 
+Peter: "Hard to say. She left in a hurry. But I might be able to help—if you help me first."
+Geralt: "Go on."
+Peter: "A griffin’s been harassing our patrols. Killed some of my men just west of here. The villagers are terrified. If you slay it, I’ll share what I know."
+Geralt: "A griffin. Means it has a lair. Any idea where?"
+Peter: "Yes, near the old mill. Found bodies torn to shreds. Could be it’s nesting in the hills nearby."
+Geralt: "I’ll need to set a trap. Buckthorn works well as bait—its scent drives them mad."
+Peter: "Buckthorn? Haven’t heard of it. Where would you find it?"
+Geralt: "Usually grows at the bottom of riverbeds. I’ll need to ask around. Someone local should know."
+Peter: "Tomira, the herbalist, lives nearby. Knows plants better than anyone. Tell her I sent you."
+Geralt: "Alright. I’ll deal with the griffin—and you’ll give me what I need on Yennefer."
+Peter: "You have my word, witcher. Kill the beast, and I’ll tell you all I know."</t>
+  </si>
+  <si>
+    <t>Write text to game Witcher 3: Wild Hunt. Your guideline:
+Creators: Geralt of Rivia, Peter Saar Gwynleve
+Type of text: Dialogue
+Length: max 300 words 
+Content:
+- List of facts that need to be contained: [“Geralt is seeking information about Yennefer of Vengerberg", "Peter offers to help in exchange for slaying a griffin that has been terrorizing the area", "The officer provides details about the griffin's lair and informs Geralt about dead soldiers", "Geralt knows he needs to set a trap for the griffin and requests buckthorn as bait", "The officer suggests visiting Tomira, an herbalist, for assistance in obtaining the herb."] 
+- Participants:  Geralt of Rivia, Peter Saar Gwynleve</t>
+  </si>
+  <si>
+    <t>Dialogue between Cerys and Udalryk, after Cerys' plan. She tries to convince him that she would never harm his child and explains her plan.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1441,13 +1607,26 @@
       <family val="2"/>
       <charset val="238"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -1459,10 +1638,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1495,8 +1675,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Dobry" xfId="1" builtinId="26"/>
     <cellStyle name="Normalny" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1510,6 +1692,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1775,6 +1961,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <tabColor theme="9" tint="0.59999389629810485"/>
+  </sheetPr>
   <dimension ref="B1:G3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1790,48 +1979,46 @@
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="1" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="D2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="5" t="s">
-        <v>5</v>
-      </c>
       <c r="E2" s="5" t="s">
-        <v>0</v>
+        <v>177</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>3</v>
+        <v>178</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="2:7" ht="173.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
-      <c r="C3" t="s">
-        <v>38</v>
-      </c>
+      <c r="C3"/>
       <c r="D3" s="5" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -1841,6 +2028,9 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DB559D6-176B-4EE2-AD2E-00482C77A0C2}">
+  <sheetPr>
+    <tabColor theme="0"/>
+  </sheetPr>
   <dimension ref="B1:G3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1856,46 +2046,46 @@
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="1" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="G2" s="5"/>
     </row>
     <row r="3" spans="2:7" ht="173.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="11" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -1920,36 +2110,36 @@
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="1" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G2" s="5"/>
     </row>
@@ -1980,46 +2170,46 @@
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="1" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="G2" s="5"/>
     </row>
     <row r="3" spans="2:7" ht="173.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="2" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -2045,36 +2235,36 @@
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="1" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="D2" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>24</v>
-      </c>
       <c r="E2" s="8" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="G2" s="5"/>
     </row>
@@ -2104,43 +2294,43 @@
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="1" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E2" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="F2" s="5" t="s">
         <v>60</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>64</v>
       </c>
       <c r="G2" s="5"/>
     </row>
     <row r="3" spans="2:7" ht="173.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D3" s="5"/>
     </row>
@@ -2151,7 +2341,10 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F9237EA-F370-4FAB-AAF8-0971670A2A45}">
-  <dimension ref="B1:G3"/>
+  <sheetPr>
+    <tabColor theme="9" tint="0.59999389629810485"/>
+  </sheetPr>
+  <dimension ref="B1:G36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="2"/>
@@ -2166,47 +2359,50 @@
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="1" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>70</v>
+        <v>166</v>
       </c>
       <c r="G2" s="5"/>
     </row>
     <row r="3" spans="2:7" ht="173.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="D3" s="5" t="s">
-        <v>67</v>
-      </c>
+    </row>
+    <row r="36" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D36" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2230,43 +2426,43 @@
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="1" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="G2" s="5"/>
     </row>
     <row r="3" spans="2:7" ht="173.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="12" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D3" s="5"/>
     </row>
@@ -2277,6 +2473,9 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11D70C3E-6BAD-4B59-A3ED-C4AAA2F0C5BB}">
+  <sheetPr>
+    <tabColor theme="9" tint="0.59999389629810485"/>
+  </sheetPr>
   <dimension ref="B1:G3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2292,43 +2491,43 @@
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="1" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>135</v>
+        <v>168</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>136</v>
+        <v>167</v>
       </c>
       <c r="G2" s="5"/>
     </row>
     <row r="3" spans="2:7" ht="173.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="12" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="D3" s="5"/>
     </row>
@@ -2354,43 +2553,43 @@
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="1" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="G2" s="5"/>
     </row>
     <row r="3" spans="2:7" ht="173.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="12" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="D3" s="5"/>
     </row>
@@ -2416,43 +2615,43 @@
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="1" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="G2" s="5"/>
     </row>
     <row r="3" spans="2:7" ht="173.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="12" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="D3" s="5"/>
     </row>
@@ -2463,6 +2662,9 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24F6BA2C-F12D-41F3-ABAC-8B20BC07BBD3}">
+  <sheetPr>
+    <tabColor theme="9" tint="0.59999389629810485"/>
+  </sheetPr>
   <dimension ref="B1:G3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2478,45 +2680,45 @@
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="1" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D2" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="F2" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="5" t="s">
         <v>8</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="3" spans="2:7" ht="173.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="D3" s="5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -2541,43 +2743,43 @@
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="1" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="C2" s="5" t="s">
-        <v>109</v>
-      </c>
       <c r="D2" s="5" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="G2" s="5"/>
     </row>
     <row r="3" spans="2:7" ht="173.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="12" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="D3" s="5"/>
     </row>
@@ -2604,43 +2806,43 @@
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="1" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="G2" s="5"/>
     </row>
     <row r="3" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="2" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="D3" s="5"/>
     </row>
@@ -2667,43 +2869,43 @@
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="1" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="G2" s="5"/>
     </row>
     <row r="3" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="2" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="D3" s="5"/>
     </row>
@@ -2729,43 +2931,43 @@
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="1" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="G2" s="5"/>
     </row>
     <row r="3" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="2" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="D3" s="5"/>
     </row>
@@ -2791,43 +2993,43 @@
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="1" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="G2" s="5"/>
     </row>
     <row r="3" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="2" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="D3" s="5"/>
     </row>
@@ -2853,43 +3055,43 @@
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="1" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="G2" s="5"/>
     </row>
     <row r="3" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="2" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="D3" s="5"/>
     </row>
@@ -2915,43 +3117,43 @@
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="1" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="G2" s="5"/>
     </row>
     <row r="3" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="2" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="D3" s="5"/>
     </row>
@@ -2962,6 +3164,9 @@
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A246A86-8DC3-4705-84B7-27D90A58A910}">
+  <sheetPr>
+    <tabColor theme="9" tint="0.59999389629810485"/>
+  </sheetPr>
   <dimension ref="B1:G3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2977,43 +3182,43 @@
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="1" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>114</v>
+        <v>170</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="G2" s="5"/>
     </row>
     <row r="3" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="2" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="D3" s="5"/>
     </row>
@@ -3039,43 +3244,43 @@
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="1" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="G2" s="5"/>
     </row>
     <row r="3" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="2" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="D3" s="5"/>
     </row>
@@ -3086,6 +3291,9 @@
 
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6EC4AAC-B61B-48EC-9A17-61611303979A}">
+  <sheetPr>
+    <tabColor theme="9" tint="0.59999389629810485"/>
+  </sheetPr>
   <dimension ref="B1:G3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3101,43 +3309,43 @@
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="1" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>120</v>
+        <v>172</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="G2" s="5"/>
     </row>
     <row r="3" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="2" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="D3" s="5"/>
     </row>
@@ -3163,46 +3371,44 @@
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="1" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>37</v>
+        <v>180</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G2" s="5"/>
     </row>
     <row r="3" spans="2:7" ht="173.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
-      <c r="C3" t="s">
-        <v>38</v>
-      </c>
+      <c r="C3"/>
       <c r="D3" s="5" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -3227,43 +3433,43 @@
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="1" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="G2" s="5"/>
     </row>
     <row r="3" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="2" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="D3" s="5"/>
     </row>
@@ -3273,6 +3479,662 @@
 </file>
 
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CE59D6F-232E-40AF-8406-C9E2D96DA95C}">
+  <sheetPr>
+    <tabColor theme="9" tint="0.59999389629810485"/>
+  </sheetPr>
+  <dimension ref="B1:G3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.140625" style="2"/>
+    <col min="2" max="2" width="58.85546875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="54.85546875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="40.42578125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="43.28515625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="42" style="2" customWidth="1"/>
+    <col min="7" max="7" width="77.85546875" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B1" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="G2" s="5"/>
+    </row>
+    <row r="3" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="3"/>
+      <c r="C3" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D3" s="5"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBB3122E-F0DD-4C11-BEC0-CB1B52D2C4A5}">
+  <dimension ref="B1:G3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.140625" style="2"/>
+    <col min="2" max="2" width="58.85546875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="54.85546875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="40.42578125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="43.28515625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="42" style="2" customWidth="1"/>
+    <col min="7" max="7" width="77.85546875" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B1" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+    </row>
+    <row r="3" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="3"/>
+      <c r="C3" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D3" s="5"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CD977C9-7C33-4666-B2DD-0A38602EBE67}">
+  <dimension ref="B1:G3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.140625" style="2"/>
+    <col min="2" max="2" width="58.85546875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="54.85546875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="40.42578125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="43.28515625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="42" style="2" customWidth="1"/>
+    <col min="7" max="7" width="77.85546875" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B1" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+    </row>
+    <row r="3" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="3"/>
+      <c r="C3" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D3" s="5"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CF51CB2-D5E4-4746-9977-AA0B5C2E7814}">
+  <dimension ref="B1:G3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.140625" style="2"/>
+    <col min="2" max="2" width="58.85546875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="54.85546875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="40.42578125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="43.28515625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="42" style="2" customWidth="1"/>
+    <col min="7" max="7" width="77.85546875" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B1" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+    </row>
+    <row r="3" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="3"/>
+      <c r="C3" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D3" s="5"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{218EDC01-E594-4798-9AAF-1DDA7B23CBB5}">
+  <dimension ref="B1:G3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.140625" style="2"/>
+    <col min="2" max="2" width="58.85546875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="54.85546875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="40.42578125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="43.28515625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="42" style="2" customWidth="1"/>
+    <col min="7" max="7" width="77.85546875" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B1" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+    </row>
+    <row r="3" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="3"/>
+      <c r="C3" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D3" s="5"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EA326F7-03AE-42D7-9FC8-672BE7E75403}">
+  <dimension ref="B1:G3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.140625" style="2"/>
+    <col min="2" max="2" width="58.85546875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="54.85546875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="40.42578125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="43.28515625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="42" style="2" customWidth="1"/>
+    <col min="7" max="7" width="77.85546875" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B1" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+    </row>
+    <row r="3" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="3"/>
+      <c r="C3" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D3" s="5"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05A9A5E6-FB61-466C-9770-D106AA28BA72}">
+  <sheetPr>
+    <tabColor theme="9" tint="0.59999389629810485"/>
+  </sheetPr>
+  <dimension ref="B1:G3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.140625" style="2"/>
+    <col min="2" max="2" width="58.85546875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="54.85546875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="40.42578125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="43.28515625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="42" style="2" customWidth="1"/>
+    <col min="7" max="7" width="77.85546875" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B1" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="G2" s="5"/>
+    </row>
+    <row r="3" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="3"/>
+      <c r="C3" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D3" s="5"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{060AA9A8-E660-44C9-A635-A120C7D00135}">
+  <dimension ref="B1:G3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.140625" style="2"/>
+    <col min="2" max="2" width="58.85546875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="54.85546875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="40.42578125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="43.28515625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="42" style="2" customWidth="1"/>
+    <col min="7" max="7" width="77.85546875" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B1" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+    </row>
+    <row r="3" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="3"/>
+      <c r="C3" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D3" s="5"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{441BE83A-14B4-4D55-8AA2-0BE473B26E25}">
+  <dimension ref="B1:G3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.140625" style="2"/>
+    <col min="2" max="2" width="58.85546875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="54.85546875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="40.42578125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="43.28515625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="42" style="2" customWidth="1"/>
+    <col min="7" max="7" width="77.85546875" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B1" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+    </row>
+    <row r="3" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="3"/>
+      <c r="C3" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D3" s="5"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A355C62-4CA2-4186-9037-C61635EDE76D}">
+  <dimension ref="B1:G3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.140625" style="2"/>
+    <col min="2" max="2" width="58.85546875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="54.85546875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="40.42578125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="43.28515625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="42" style="2" customWidth="1"/>
+    <col min="7" max="7" width="77.85546875" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B1" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="G2" s="5"/>
+    </row>
+    <row r="3" spans="2:7" ht="173.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="3"/>
+      <c r="C3"/>
+      <c r="D3" s="5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C96C6F6-98D7-481B-ADB3-D7D47C7E42D2}">
+  <dimension ref="B1:G3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.140625" style="2"/>
+    <col min="2" max="2" width="58.85546875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="54.85546875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="40.42578125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="43.28515625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="42" style="2" customWidth="1"/>
+    <col min="7" max="7" width="77.85546875" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B1" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+    </row>
+    <row r="3" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="3"/>
+      <c r="C3" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D3" s="5"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D1C650B-E38C-4A4A-9CC0-12F2F98BB1C4}">
   <sheetPr codeName="Arkusz5"/>
   <dimension ref="B1:G3"/>
@@ -3290,29 +4152,29 @@
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="1" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="6"/>
       <c r="C2" s="5"/>
       <c r="D2" s="5" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
@@ -3320,70 +4182,6 @@
     <row r="3" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="D3" s="5"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A355C62-4CA2-4186-9037-C61635EDE76D}">
-  <dimension ref="B1:G3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="9.140625" style="2"/>
-    <col min="2" max="2" width="58.85546875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="54.85546875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="40.42578125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="43.28515625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="42" style="2" customWidth="1"/>
-    <col min="7" max="7" width="77.85546875" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B1" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="G2" s="5"/>
-    </row>
-    <row r="3" spans="2:7" ht="173.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="3"/>
-      <c r="C3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>5</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3407,46 +4205,46 @@
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="1" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G2" s="5"/>
     </row>
     <row r="3" spans="2:7" ht="173.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="11" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -3471,43 +4269,43 @@
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="1" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D2" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2" s="5" t="s">
         <v>51</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>55</v>
       </c>
       <c r="G2" s="5"/>
     </row>
     <row r="3" spans="2:7" ht="173.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="11" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D3" s="5"/>
     </row>
@@ -3533,51 +4331,51 @@
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="1" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E2" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="F2" s="5" t="s">
         <v>84</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>89</v>
       </c>
       <c r="G2" s="5"/>
     </row>
     <row r="3" spans="2:7" ht="73.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="11" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4" spans="2:7" ht="285" x14ac:dyDescent="0.25">
       <c r="D4" s="13" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -3603,46 +4401,44 @@
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="1" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G2" s="5"/>
     </row>
     <row r="3" spans="2:7" ht="173.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
-      <c r="C3" s="11" t="s">
-        <v>38</v>
-      </c>
+      <c r="C3" s="11"/>
       <c r="D3" s="5" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -3667,46 +4463,44 @@
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="1" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="E2" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="F2" s="5" t="s">
         <v>90</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>95</v>
       </c>
       <c r="G2" s="5"/>
     </row>
     <row r="3" spans="2:7" ht="173.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
-      <c r="C3" s="11" t="s">
-        <v>38</v>
-      </c>
+      <c r="C3" s="11"/>
       <c r="D3" s="5" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -3715,21 +4509,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F0D812EB0939BE44B372FF1F45A9F73C" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="b279ff35aeca1c14d8137b0da22afbf9">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="63d4114e-1bef-4718-838e-9be3cc0e7df4" xmlns:ns4="89118cec-cb09-49c5-a79b-3d4b3e9d9980" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2c90ea5fa4cf6378d877eb3f32d57d39" ns3:_="" ns4:_="">
     <xsd:import namespace="63d4114e-1bef-4718-838e-9be3cc0e7df4"/>
@@ -3926,32 +4705,22 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0A8ED665-E737-40E7-B55A-D5579DF920C2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CEFB7BEA-F1DC-4002-BBA4-F3BBCE3A973D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="89118cec-cb09-49c5-a79b-3d4b3e9d9980"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="63d4114e-1bef-4718-838e-9be3cc0e7df4"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{53F54199-27FD-4E4A-88C4-16904FF3AA53}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3968,4 +4737,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CEFB7BEA-F1DC-4002-BBA4-F3BBCE3A973D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="89118cec-cb09-49c5-a79b-3d4b3e9d9980"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="63d4114e-1bef-4718-838e-9be3cc0e7df4"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0A8ED665-E737-40E7-B55A-D5579DF920C2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/witcher_info.xlsx
+++ b/witcher_info.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Magisterka\Magisterka\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F62DAB6C-3E53-4665-9EE6-1269F2AEC197}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2380DB0-5B6A-43C2-A230-D9E8D2621150}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="31" activeTab="36" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="D_NilfgardOficer" sheetId="1" r:id="rId1"/>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="182">
   <si>
     <t>After rescuing the merchant Bram from the clutches of a rabid royal griffin, the two witches of the Wolf Guild school, Geralt of Rivia and his master Vesemir, were directed to an inn in White Orchard so that there they could inquire about the woman they were looking for, the sorceress Yennefer. So the monster slayers went to the inn where they asked the travelers about Geralt's beloved. There the Witcher Geralt met Professor Aldert Geert, who introduced him to the game of threads, and also listened to local superstitions about the Harbinger of War. However, he received real information about his beloved from a wandering merchant, Gaunter o'Dima, who directed him to a fortress where a Nilfgaard garrison was set up, claiming that a scout there had recently seen the sorceress[1]. Geralt went to the indicated place where he made a deal with Captain Peter Saar Gwynlew. The captain promised to give the witcher information about Yennefer if he would slaughter the enraged royal griffin. He also directed him to the herbalist Tomira and the hunter Myslaw, who were to help him prepare for the hunt. Geralt met Myslaw during his hunt for feral dogs that were threatening people in the area[1].Myslaw gladly accepted the witcher's help and together they took care of the animals. They also found the corpse of Pieter, a stable boy who years ago revealed his relationship with Florian to the heir. The hunter could then tell Geralt his story and explain why he had been banished from the village. After this, he led Geralt to the site of the murder of the Nilfgaard soldiers, where he parted ways with the monster slayer[1].Walking up the hill, the witcher found the destroyed nest of a griffin, in which lay a slain female. He guessed that the individual who was terrorizing the area was a desperate male royal griffin, as well as what the Nilfgaardians had done to its nest in an attempt to get rid of the monster. Geralt then went to the local herbalist Tomira, who had just taken care of the griffin-injured Lena. The monster slayer learned from the herbalist where he would find the sagebrush he needed to make a trap for the monster. After gathering information about the beast and the necessary ingredients, the witcher returned to Vesemir and together they prepared the ambush. The griffin sensed the jackal and arrived on the scene after just a moment. The two of them dealt with the monster, after which Geralt carried its head to the Nilfgaard captain as proof that he had fulfilled his part of the bargain. Peter Saar Gwynlew gave the witcher information about Yennefer, and the witcher, furious that he had wasted so much time in the village, returned to give a new lead to Vesemir[1]. The Witchers met again at the inn, but there a brawl ensued in which one of the women accused the innkeeper Elza of collaborating with Nilfgaard. Geralt and Vesemir stepped forward to defend the attacked innkeeper, to which a bunch of drunken peasants reacted with aggression. Faced with the threat, the witches were thus forced to draw their steel swords. After a bloody showdown with the peasants, the witches were chased out of the inn by Elza, in whose defense they stood. So the Witchers left White Orchard[1].</t>
   </si>
@@ -79,11 +79,6 @@
   </si>
   <si>
     <t>Peter Saar Gwynleve was the captain of the Nilfgaardian Garrison located in White Orchard. By all appearances he seemed a rather fair and kind person to the people of White Orchard, especially by the standards of most conquering Nilfgaardians.</t>
-  </si>
-  <si>
-    <t>Geralt is looking for Yennefer and encounters Gaunter, who offers to help. Gaunter mentions that a 
-  Nilfgaardian scout saw Yennefer at their camp, where she had a brief conversation with the garrison commander before leaving. 
-  Geralt is advised to ask at the garrison for more information. Gaunter expresses that witcher maybe help him in the future.</t>
   </si>
   <si>
     <t>Geralt: Looking for a woman.
@@ -713,9 +708,6 @@
 The quest, or this first part of it, completes when Geralt has all 3 keys and unlocks the safe with a nice treasure for his trouble.</t>
   </si>
   <si>
-    <t>Message from Fritz to Wallter and Lussi, about problem with buesiness and his idea of three key chest for their treasure.</t>
-  </si>
-  <si>
     <t>Widower, 60 years of age, of medium height, above-average intellect, possessing a fortune in both species and real estate, seeks old maid or childless widow of a similar age or somewhat older, preferably from a landed family. Those interested are requested to send a missive with a (faithful!) engraving of their likeness included, to Poste Restante Gildorf, c/o "Romantic."
 P.S. No response will be given to letters without a full name and valid return address.
 P.P.S. Women of the elder races, halflings in particular, need not inquire.</t>
@@ -1440,15 +1432,6 @@
 </t>
   </si>
   <si>
-    <t>Write text to game Witcher 3: Wild Hunt. Your guideline:
-Creators: Book Author
-Type of text: Book Page
-Length: max 400 words 
-Content:
--  Thmetic: Elder Races
--  Tone: Scientific text</t>
-  </si>
-  <si>
     <t>In their relentless pursuit of Ciri, Geralt and Yennefer uncover troubling news: Ciri has returned to the Isles, accompanied by a masked mage. The two set sail, vanishing into the unknown. Days later, their boat drifts ashore—empty, save for a mindless creature babbling incoherently. A dark shiver runs through the Witcher and sorceress alike, for this eerie passenger hints at a fate worse than death.</t>
   </si>
   <si>
@@ -1464,15 +1447,6 @@
     <t>Ge'els, noble and proud, learns the bitter truth—Eredin, the supposed savior, is a regicide. Struck by the betrayal, Ge'els swears to aid Geralt, vowing to stand against the tyrant who stained their realm with blood.</t>
   </si>
   <si>
-    <t>Write text to game Witcher 3: Wild Hunt. Your guideline:
-Creators: Dandelion
-Type of text: Narration
-Length: max 40 words 
- Content:
--    List of facts that need to be contained: [“Convincing Ge'els to betray Eredin because he is regicide.", "Ge'els agrees"] 
- -    Participants: Ge'el</t>
-  </si>
-  <si>
     <t>Crach an Craite, Jarl of the powerful Clan an Craite, stands as one of the most respected and influential leaders on the Skellige Isles. Renowned for his unyielding spirit and unwavering loyalty, he commands not just his clan but garners the respect of rival jarls as well. Known for his fierce sense of honor and battle prowess, Crach is also a trusted ally of Geralt of Rivia. Their bond, forged through shared trials and mutual respect, traces back to Crach’s steadfast support during Geralt’s previous visits to Skellige. Though rough around the edges, Crach’s heart beats for his people, his family, and the isles he holds dear. A loyal friend but a fearsome enemy, the Jarl’s name is synonymous with Skellige’s indomitable spirit.</t>
   </si>
   <si>
@@ -1486,15 +1460,6 @@
   </si>
   <si>
     <t>Sylvans—tricksters, pranksters, and notorious gluttons—are rare creatures often mistaken for demons. Though not inherently evil, their fondness for mischief can lead to chaos, especially when they meddle in human affairs. As one old Skellige saying goes: 'A Sylvan’s jest leaves your barn empty and your head aching.' Best to treat them with caution—or better yet, a hefty offering of grain.</t>
-  </si>
-  <si>
-    <t>Write text to game Witcher 3: Wild Hunt. Your guideline:
-Creators: Dandelion
-Type of text: Bestiary Note
-Length: max 80 words 
- Content:
--    List of facts that need to be contained: ["Quote about Sylvan"] 
--    Thematic: Sylvan</t>
   </si>
   <si>
     <t>Geralt: Geralt of Rivia. Witcher.
@@ -1531,16 +1496,63 @@
 Peter: "You have my word, witcher. Kill the beast, and I’ll tell you all I know."</t>
   </si>
   <si>
+    <t>Dialogue between Cerys and Udalryk, after Cerys' plan. She tries to convince him that she would never harm his child and explains her plan.</t>
+  </si>
+  <si>
+    <t>hmm</t>
+  </si>
+  <si>
+    <t>Write text to game Witcher 3: Wild Hunt. Your guideline:
+Creators: Gaunter O'Dim, Geralt of Rivia
+Type of text: Dialogues
+Length: max 250 words
+Content:
+-  List of  facts that need to be contained: [“Geralt is looking for Yennefer”, "Gounter offers help",  "Nilfgaardian scout saw Yennefer at their camp, where she had a brief conversation with the garrison commander before leaving.", "Gaunter expresses that witcher maybe help him in the future."]
+-  Participants: Gaunter O'Dim, Geralt of Rivia</t>
+  </si>
+  <si>
     <t>Write text to game Witcher 3: Wild Hunt. Your guideline:
 Creators: Geralt of Rivia, Peter Saar Gwynleve
 Type of text: Dialogue
-Length: max 300 words 
+Length: max 300 words
 Content:
-- List of facts that need to be contained: [“Geralt is seeking information about Yennefer of Vengerberg", "Peter offers to help in exchange for slaying a griffin that has been terrorizing the area", "The officer provides details about the griffin's lair and informs Geralt about dead soldiers", "Geralt knows he needs to set a trap for the griffin and requests buckthorn as bait", "The officer suggests visiting Tomira, an herbalist, for assistance in obtaining the herb."] 
+- List of facts that need to be contained: [“Geralt is seeking information about Yennefer of Vengerberg", "Peter offers to help in exchange for slaying a griffin that has been terrorizing the area", "The officer provides details about the griffin's lair and informs Geralt about dead soldiers", "Geralt knows he needs to set a trap for the griffin and requests buckthorn as bait", "The officer suggests visiting Tomira, an herbalist, for assistance in obtaining the herb."]
 - Participants:  Geralt of Rivia, Peter Saar Gwynleve</t>
   </si>
   <si>
-    <t>Dialogue between Cerys and Udalryk, after Cerys' plan. She tries to convince him that she would never harm his child and explains her plan.</t>
+    <t>Write text to game Witcher 3: Wild Hunt. Your guideline: 
+Creators: Fritz Type of text: Letter 
+Length: max 200 words 
+Content: 
+-    List of facts that need to be contained: [“Fritz writes to Wallter and Lussi, about problem with buesiness and his idea of three key chest for their treasure.", "Loot is currently at his Firtz's place but he don't want to trick them"] 
+ -    Participants: Wallter, Lussi, Fritz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Write text to game Witcher 3: Wild Hunt. Your guideline: 
+Creators: Book Author 
+Type of text: Book Page 
+Length: max 400 words 
+Content: 
+- Thmetic: Elder Races 
+- Tone: Scientific text  </t>
+  </si>
+  <si>
+    <t>Write text to game Witcher 3: Wild Hunt. Your guideline:
+Creators: Dandelion
+Type of text:
+Narration Length: max 40 words
+ Content:
+- List of facts that need to be contained: [“Convincing Ge'els to betray Eredin because he is regicide.", "Ge'els agrees"]
+ - Participants: Ge'el</t>
+  </si>
+  <si>
+    <t>Write text to game Witcher 3: Wild Hunt. Your guideline:
+Creators: Dandelion
+Type of text: Bestiary Note
+Length: max 80 words
+ Content:
+-    List of facts that need to be contained: ["Quote about Sylvan"]
+-    Thematic: Sylvan</t>
   </si>
 </sst>
 </file>
@@ -1692,10 +1704,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1964,7 +1972,7 @@
   <sheetPr>
     <tabColor theme="9" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="B1:G3"/>
+  <dimension ref="B1:G7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="2"/>
@@ -1979,19 +1987,19 @@
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D1" s="7" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1999,19 +2007,19 @@
         <v>0</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>2</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="2:7" ht="173.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2019,6 +2027,11 @@
       <c r="C3"/>
       <c r="D3" s="5" t="s">
         <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="E7" s="2" t="s">
+        <v>175</v>
       </c>
     </row>
   </sheetData>
@@ -2046,46 +2059,46 @@
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D1" s="7" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D2" s="10" t="s">
         <v>2</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="G2" s="5"/>
     </row>
     <row r="3" spans="2:7" ht="173.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -2110,36 +2123,36 @@
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D1" s="7" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="5" t="s">
         <v>11</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>12</v>
       </c>
       <c r="G2" s="5"/>
     </row>
@@ -2170,46 +2183,46 @@
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D1" s="7" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="G2" s="5"/>
     </row>
     <row r="3" spans="2:7" ht="173.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -2235,36 +2248,36 @@
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D1" s="7" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G2" s="5"/>
     </row>
@@ -2294,43 +2307,43 @@
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D1" s="7" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G2" s="5"/>
     </row>
     <row r="3" spans="2:7" ht="173.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D3" s="5"/>
     </row>
@@ -2359,46 +2372,46 @@
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D1" s="7" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>65</v>
+        <v>178</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="G2" s="5"/>
     </row>
     <row r="3" spans="2:7" ht="173.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="36" spans="4:4" x14ac:dyDescent="0.25">
@@ -2426,43 +2439,43 @@
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D1" s="7" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C2" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2" s="5" t="s">
         <v>68</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>70</v>
       </c>
       <c r="G2" s="5"/>
     </row>
     <row r="3" spans="2:7" ht="173.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D3" s="5"/>
     </row>
@@ -2491,43 +2504,43 @@
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D1" s="7" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="G2" s="5"/>
     </row>
     <row r="3" spans="2:7" ht="173.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="12" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D3" s="5"/>
     </row>
@@ -2553,43 +2566,43 @@
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D1" s="7" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="D2" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="E2" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="F2" s="5" t="s">
         <v>128</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>130</v>
       </c>
       <c r="G2" s="5"/>
     </row>
     <row r="3" spans="2:7" ht="173.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="12" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D3" s="5"/>
     </row>
@@ -2615,43 +2628,43 @@
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D1" s="7" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="D2" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="C2" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>101</v>
-      </c>
       <c r="E2" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G2" s="5"/>
     </row>
     <row r="3" spans="2:7" ht="173.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="12" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D3" s="5"/>
     </row>
@@ -2680,19 +2693,19 @@
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D1" s="7" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2700,25 +2713,25 @@
         <v>0</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>4</v>
+        <v>176</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>2</v>
       </c>
       <c r="E2" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="5" t="s">
-        <v>6</v>
-      </c>
       <c r="G2" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="2:7" ht="173.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="D3" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -2743,43 +2756,43 @@
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D1" s="7" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G2" s="5"/>
     </row>
     <row r="3" spans="2:7" ht="173.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="12" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D3" s="5"/>
     </row>
@@ -2806,19 +2819,19 @@
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D1" s="7" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2826,23 +2839,23 @@
         <v>0</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G2" s="5"/>
     </row>
     <row r="3" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D3" s="5"/>
     </row>
@@ -2869,43 +2882,43 @@
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D1" s="7" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="5" t="s">
-        <v>26</v>
-      </c>
       <c r="D2" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="G2" s="5"/>
     </row>
     <row r="3" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D3" s="5"/>
     </row>
@@ -2931,43 +2944,43 @@
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D1" s="7" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G2" s="5"/>
     </row>
     <row r="3" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D3" s="5"/>
     </row>
@@ -2993,43 +3006,43 @@
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D1" s="7" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="G2" s="5"/>
     </row>
     <row r="3" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D3" s="5"/>
     </row>
@@ -3055,43 +3068,43 @@
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D1" s="7" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G2" s="5"/>
     </row>
     <row r="3" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D3" s="5"/>
     </row>
@@ -3117,43 +3130,43 @@
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D1" s="7" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="G2" s="5"/>
     </row>
     <row r="3" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D3" s="5"/>
     </row>
@@ -3182,43 +3195,43 @@
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D1" s="7" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="G2" s="5"/>
     </row>
     <row r="3" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D3" s="5"/>
     </row>
@@ -3244,43 +3257,43 @@
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D1" s="7" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G2" s="5"/>
     </row>
     <row r="3" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D3" s="5"/>
     </row>
@@ -3309,43 +3322,43 @@
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D1" s="7" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="G2" s="5"/>
     </row>
     <row r="3" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D3" s="5"/>
     </row>
@@ -3371,36 +3384,36 @@
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D1" s="7" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G2" s="5"/>
     </row>
@@ -3408,7 +3421,7 @@
       <c r="B3" s="3"/>
       <c r="C3"/>
       <c r="D3" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -3433,43 +3446,43 @@
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D1" s="7" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G2" s="5"/>
     </row>
     <row r="3" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D3" s="5"/>
     </row>
@@ -3498,43 +3511,43 @@
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D1" s="7" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="G2" s="5"/>
     </row>
     <row r="3" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D3" s="5"/>
     </row>
@@ -3560,31 +3573,31 @@
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D1" s="7" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
@@ -3592,7 +3605,7 @@
     <row r="3" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D3" s="5"/>
     </row>
@@ -3618,31 +3631,31 @@
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D1" s="7" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
@@ -3650,7 +3663,7 @@
     <row r="3" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D3" s="5"/>
     </row>
@@ -3676,31 +3689,31 @@
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D1" s="7" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
@@ -3708,7 +3721,7 @@
     <row r="3" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D3" s="5"/>
     </row>
@@ -3734,31 +3747,31 @@
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D1" s="7" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
@@ -3766,7 +3779,7 @@
     <row r="3" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D3" s="5"/>
     </row>
@@ -3792,31 +3805,31 @@
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D1" s="7" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
@@ -3824,7 +3837,7 @@
     <row r="3" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D3" s="5"/>
     </row>
@@ -3853,43 +3866,43 @@
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D1" s="7" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="G2" s="5"/>
     </row>
     <row r="3" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D3" s="5"/>
     </row>
@@ -3915,31 +3928,31 @@
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D1" s="7" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
@@ -3947,7 +3960,7 @@
     <row r="3" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D3" s="5"/>
     </row>
@@ -3973,31 +3986,31 @@
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D1" s="7" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
@@ -4005,7 +4018,7 @@
     <row r="3" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D3" s="5"/>
     </row>
@@ -4031,36 +4044,36 @@
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D1" s="7" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="D2" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="F2" s="5" t="s">
         <v>39</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>40</v>
       </c>
       <c r="G2" s="5"/>
     </row>
@@ -4093,31 +4106,31 @@
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D1" s="7" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
@@ -4125,7 +4138,7 @@
     <row r="3" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D3" s="5"/>
     </row>
@@ -4152,29 +4165,29 @@
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D1" s="7" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="6"/>
       <c r="C2" s="5"/>
       <c r="D2" s="5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
@@ -4205,43 +4218,43 @@
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D1" s="7" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C2" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="F2" s="5" t="s">
         <v>42</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>43</v>
       </c>
       <c r="G2" s="5"/>
     </row>
     <row r="3" spans="2:7" ht="173.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>2</v>
@@ -4269,43 +4282,43 @@
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D1" s="7" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C2" s="5" t="s">
-        <v>49</v>
-      </c>
       <c r="D2" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G2" s="5"/>
     </row>
     <row r="3" spans="2:7" ht="173.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D3" s="5"/>
     </row>
@@ -4331,51 +4344,51 @@
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D1" s="7" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>2</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G2" s="5"/>
     </row>
     <row r="3" spans="2:7" ht="73.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="2:7" ht="285" x14ac:dyDescent="0.25">
       <c r="D4" s="13" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -4401,36 +4414,36 @@
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D1" s="7" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="D2" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="F2" s="5" t="s">
         <v>54</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>55</v>
       </c>
       <c r="G2" s="5"/>
     </row>
@@ -4463,36 +4476,36 @@
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D1" s="7" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G2" s="5"/>
     </row>
@@ -4500,7 +4513,7 @@
       <c r="B3" s="3"/>
       <c r="C3" s="11"/>
       <c r="D3" s="5" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -4509,6 +4522,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F0D812EB0939BE44B372FF1F45A9F73C" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="b279ff35aeca1c14d8137b0da22afbf9">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="63d4114e-1bef-4718-838e-9be3cc0e7df4" xmlns:ns4="89118cec-cb09-49c5-a79b-3d4b3e9d9980" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2c90ea5fa4cf6378d877eb3f32d57d39" ns3:_="" ns4:_="">
     <xsd:import namespace="63d4114e-1bef-4718-838e-9be3cc0e7df4"/>
@@ -4705,22 +4733,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CEFB7BEA-F1DC-4002-BBA4-F3BBCE3A973D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="89118cec-cb09-49c5-a79b-3d4b3e9d9980"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="63d4114e-1bef-4718-838e-9be3cc0e7df4"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0A8ED665-E737-40E7-B55A-D5579DF920C2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{53F54199-27FD-4E4A-88C4-16904FF3AA53}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4737,29 +4775,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CEFB7BEA-F1DC-4002-BBA4-F3BBCE3A973D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="89118cec-cb09-49c5-a79b-3d4b3e9d9980"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="63d4114e-1bef-4718-838e-9be3cc0e7df4"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0A8ED665-E737-40E7-B55A-D5579DF920C2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/witcher_info.xlsx
+++ b/witcher_info.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Magisterka\Magisterka\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2380DB0-5B6A-43C2-A230-D9E8D2621150}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{212B0A77-DE73-4EEE-A9EA-AE0FD89CD843}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="29" activeTab="31" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="D_NilfgardOficer" sheetId="1" r:id="rId1"/>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="181">
   <si>
     <t>After rescuing the merchant Bram from the clutches of a rabid royal griffin, the two witches of the Wolf Guild school, Geralt of Rivia and his master Vesemir, were directed to an inn in White Orchard so that there they could inquire about the woman they were looking for, the sorceress Yennefer. So the monster slayers went to the inn where they asked the travelers about Geralt's beloved. There the Witcher Geralt met Professor Aldert Geert, who introduced him to the game of threads, and also listened to local superstitions about the Harbinger of War. However, he received real information about his beloved from a wandering merchant, Gaunter o'Dima, who directed him to a fortress where a Nilfgaard garrison was set up, claiming that a scout there had recently seen the sorceress[1]. Geralt went to the indicated place where he made a deal with Captain Peter Saar Gwynlew. The captain promised to give the witcher information about Yennefer if he would slaughter the enraged royal griffin. He also directed him to the herbalist Tomira and the hunter Myslaw, who were to help him prepare for the hunt. Geralt met Myslaw during his hunt for feral dogs that were threatening people in the area[1].Myslaw gladly accepted the witcher's help and together they took care of the animals. They also found the corpse of Pieter, a stable boy who years ago revealed his relationship with Florian to the heir. The hunter could then tell Geralt his story and explain why he had been banished from the village. After this, he led Geralt to the site of the murder of the Nilfgaard soldiers, where he parted ways with the monster slayer[1].Walking up the hill, the witcher found the destroyed nest of a griffin, in which lay a slain female. He guessed that the individual who was terrorizing the area was a desperate male royal griffin, as well as what the Nilfgaardians had done to its nest in an attempt to get rid of the monster. Geralt then went to the local herbalist Tomira, who had just taken care of the griffin-injured Lena. The monster slayer learned from the herbalist where he would find the sagebrush he needed to make a trap for the monster. After gathering information about the beast and the necessary ingredients, the witcher returned to Vesemir and together they prepared the ambush. The griffin sensed the jackal and arrived on the scene after just a moment. The two of them dealt with the monster, after which Geralt carried its head to the Nilfgaard captain as proof that he had fulfilled his part of the bargain. Peter Saar Gwynlew gave the witcher information about Yennefer, and the witcher, furious that he had wasted so much time in the village, returned to give a new lead to Vesemir[1]. The Witchers met again at the inn, but there a brawl ensued in which one of the women accused the innkeeper Elza of collaborating with Nilfgaard. Geralt and Vesemir stepped forward to defend the attacked innkeeper, to which a bunch of drunken peasants reacted with aggression. Faced with the threat, the witches were thus forced to draw their steel swords. After a bloody showdown with the peasants, the witches were chased out of the inn by Elza, in whose defense they stood. So the Witchers left White Orchard[1].</t>
   </si>
@@ -164,19 +164,6 @@
 During combat alghouls and cemetaurs try risky maneuvers aimed at knocking their opponents to the ground so the others can finish the job by tearing them to shreds. Like a normal ghoul, an injured alghoul can fall into a frenzy and attack with blind fury. An experienced witcher knows to get out of its way on such occasions and strike from behind, while for an inexperienced witcher, such a turn of events often marks the end of his Path.</t>
   </si>
   <si>
-    <t>Field Notes – On the Physiology and Behavior of Ghouls and Alghouls
-By Naturalist Mertan of Oxenfurt, Faculty of Monstrous Biology
-Contrary to common peasant belief, ghouls are not undead but are classified as necrophages—organisms that feed on carrion. They are highly adaptable scavengers, often found on battlefields, in cemeteries, and near mass graves. While primarily nocturnal, ghouls are known to hunt in overcast daylight when blood is fresh in the air.
-A typical ghoul possesses a lean, sinewy frame, elongated limbs, and exceptional speed. Their sense of smell is acute, allowing them to detect blood from a great distance. Though lacking higher reasoning, they exhibit rudimentary pack coordination and a clear dominance structure. Direct engagement is ill-advised unless the subject is well-armed and trained.
-Alghouls, on the other hand, are a more evolved or perhaps mutated strain. They are larger, more aggressive, and distinguished by hardened keratinous growths along the back and forearms, often raised in a threat display. An enraged alghoul is especially dangerous—entering a berserker-like state in which pain sensitivity appears suppressed.
-Alghouls exhibit territorial behavior, often dominating ghoul packs. I posit they possess a limited intelligence, enough to assess threat levels and prioritize targets. Anecdotal evidence suggests they are resistant to superficial damage and must be subdued using superior force or magical disruption (notably the Aard Sign).
-Both species respond negatively to Necrophage Oil, and are susceptible to fire and blunt trauma when properly exposed. Dissection of deceased specimens reveals a diet strictly composed of decomposing organic matter, including human remains.
-In conclusion, while ghouls are pests, alghouls are predators. Treat both with respect, or preferably, from a distance behind a well-built palisade.</t>
-  </si>
-  <si>
-    <t>Note about Ghouls and Alghouls, that is written as in game world as a scientific description</t>
-  </si>
-  <si>
     <t>You will no doubt call me a liar, a cheat and a madman. You will shake your head in pity and snort in disbelief. But I promise you, I swear by all the gods: everything which you shall read in the pages to follow is the truth, the whole truth and nothing but the truth.
 I met the vampire of which I write years ago, in an inn in Beauclair. He introduced himself to me as Regis and said he was a barber and a medic. Since he looked in every aspect like a mortal man, I might never have even suspected his true nature - had not a fire broken out shortly thereafter in the establishment in which we were residing. This Regis, if that truly was his name, stood completely untouched by the flames, whereas my own clothing quickly caught fire. The vampire carried me out of the burning inn, saving my life from certain death, then treated my numerous wounds.
 At first Regis refused to answer my query as to how he had miraculously survived the furnace-like temperatures inside the burning inn without so much as a scratch on his body or a hair singed on his head. Eventually, however, he must have sensed I was a man of the world, one who would not jump to hasty judgments based on appearance or species, and revealed his identity - along with a great number of highly interesting facts.
@@ -210,16 +197,10 @@
     <t>Was write by Dying of old age man</t>
   </si>
   <si>
-    <t>An introduction to the story set in White Orchard</t>
-  </si>
-  <si>
     <t>After many trials and tribulations, Geralt finally learned that Yen was in nearby Vizima.</t>
   </si>
   <si>
     <t>Vesemir and Geralt make their way to White Orchard where they learn that Yennefer was last seen speaking with the Nilfgaardian Captain Peter Saar Gwynleve before she raced off. The captain agrees to tell Geralt where Yennefer went in exchange for ridding the town of a griffin that has recently been attacking villagers on the main road. Geralt examines the beast's nest and sets a trap for the griffin and with the help of Vesemir soon defeats the griffin. The Nilfgaardian captain says that Yennefer has rode on to Vizima. Just as Geralt and Vesemir are about to depart they are approached by none other than Yennefer herself. Yennefer insists that Geralt follow her back to Vizima for an audience with Emperor Emhyr var Emreis. Vesemir decides it would be best if he returned to Kaer Morhen.</t>
-  </si>
-  <si>
-    <t>Witcher get information about Yennefer location</t>
   </si>
   <si>
     <t>Prompt</t>
@@ -245,22 +226,6 @@
 Udalryk: On the other hand, I've known you since you were a child… You're Crach's daughter.
 Udalryk: I know you've never harmed another mindfully…
 Udalryk: Argh, let's leave it be, leave it be.</t>
-  </si>
-  <si>
-    <r>
-      <t>Udalryk an Brokvar</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="238"/>
-      </rPr>
-      <t> was the jarl of Clan Brokvar from Spikeroog in Skellige Islands. dalryk was born as the eldest son of the Jarl of Spikeroog though was soon joined by a younger brother, Aki. While the two got along well enough, their father appeared to favor Aki, going as far as bestowing the family's heirloom sword Brokvar on the younger son rather than following Skelligan custom and giving it to the firstborn son, which was considered to be a serious insult to Udalryk. Enraged at this, Udalryk publicly questioned his father's decision, breaking one of Skellige's sacred laws in doing so, and was subsequently punished by being chained to a pile in the sea for three days. Afterwards, to try and make amends, he and Aki went out on a sailing trip near Ulula's Needle when a storm broke out and Aki fell overboard. Udalryk, who had his hands full with the sails, didn't hear his brother's cry for help until it was too late and Aki drowned.
-Having failed to save his brother, Udalryk was overcome with immense guilt and sometime afterwards began to hear voices in his sleep that claimed they were messengers from the gods. These voices plagued Udalryk with strange visions and commanded he harm himself as a sacrifice to the gods, like cutting himself deep enough to leave scars, though he viewed this as a gift to hear from the gods so directly.
-Eventually he became the jarl of Clan Brokvar and by 1272 had his own son, who he named Aki in honor of his deceased brother.</t>
-    </r>
   </si>
   <si>
     <t>Cerys an Craite, aka "Sparrowhawk", was the daughter of Crach an Craite, and Hjalmar's younger sister. The young woman was a courageous Skelliger like her father and had inherited all his stubbornness. She was very self-confident and always ready to prove she could fulfill any task as good as a man, which caused her and Hjalmar to have a constant, but good-natured, rivalry. However, unlike her brother, she appeared more levelheaded, choosing to investigate and think things through first before jumping to conclusions. in: Skelligers, Humans, The Witcher 3 characters
@@ -329,42 +294,6 @@
     <t>Write a scene (only dialogues) it's description:</t>
   </si>
   <si>
-    <t>Udalryk:
-Begone, Cerys. You’ve done enough.
-Cerys:
-Please, Udalryk, just listen. I never meant to hurt your son. You know that.
-Udalryk:
-Never meant? You almost killed him! What were you thinking?
-Cerys:
-It was a trick, a necessary one. The hym fed on your guilt, and it would never leave on its own. We had to make it believe Geralt had killed the child.
-Udalryk:
-And if you were wrong? If the creature didn’t leave? My boy would be dead!
-Cerys:
-I wouldn’t have let it come to that. There was a door behind the oven, on the other side. I would have pulled the babe out the moment the hym took the bait. Not a hair on his head would’ve been singed.
-Udalryk:
-But... you didn’t know. You couldn’t know for sure.
-Cerys:
-I took a risk because there was no other way. If the hym didn’t believe the child was dead, it would never leave you. I couldn’t just stand by and let that thing destroy you, Udalryk. You’ve suffered enough.
-Udalryk:
-(sighs)
-And you’re sure? The creature... it’s really gone?
-Cerys:
-It’s gone. Geralt made sure of it. You’re free now. Free from the guilt, the nightmares.
-Udalryk:
-(pauses, looking down at his son)
-I... I’ve known you since you were a child. Crach’s daughter. You’ve always had a fierce heart. I know you’d never harm anyone mindfully... but this...
-Cerys:
-I did what had to be done. I’d never forgive myself if anything had happened to your boy. But I had to try. For you.
-Udalryk:
-(softly)
-I want to believe you. It’s just... hard to see the good in it after all that’s happened.
-Cerys:
-I understand. But you’re free now. Your son’s safe. That’s all that matters.
-Udalryk:
-(quietly)
-Aye. Maybe you’re right. Let’s... leave it be.</t>
-  </si>
-  <si>
     <t>Geralt: Been thinking… We gonna swim across the pond?
 Lambert: No, I got a boat moored there. You know, for fishing.
 Geralt: Wow… Never took you for the fishing type.
@@ -398,75 +327,6 @@
 </t>
   </si>
   <si>
-    <t>Gerlat and Lambert talk about going across the lake. Lambert have boat but it is not in great state. Dialogues continue on boat.</t>
-  </si>
-  <si>
-    <t>Geralt:
-That... thing’s your boat?
-Lambert:
-It floats. Mostly.
-Geralt:
-Barely. You sure it won’t sink halfway across?
-Lambert:
-What, don’t trust my sailing skills?
-Geralt:
-Trust your skills, not your taste in boats.
-Lambert:
-(grins)
-Could’ve walked around the lake if you wanted to. But no, gotta complain.
-Geralt:
-Thought you said it’d be faster.
-Lambert:
-It will be. As long as the lake doesn’t swallow us first.
-Geralt:
-Comforting.
-Lambert:
-(grunting)
-Come on, you piece of crap...
-Geralt:
-Maybe if you patched the holes, it’d actually move.
-Lambert:
-Nah. Keeps me awake. That, and bailing water.
-Geralt:
-Just say you’re too lazy to fix it.
-Lambert:
-Hey, it’s rustic. Got character. You like that, don’t you?
-Geralt:
-Not when it smells like fish and mold.
-Lambert:
-(snorts)
-Like you smell any better after fighting drowners.
-Geralt:
-Touché.
-Geralt:
-You ever think about getting a real boat? One that doesn’t look like it’s held together with spit and prayers?
-Lambert:
-And where’s the fun in that? Adventure, Geralt. Makes you appreciate solid ground.
-Geralt:
-And ale. Warm fire. Bed that doesn’t sway.
-Lambert:
-(raises an eyebrow)
-Starting to sound like Vesemir.
-Geralt:
-That bad?
-Lambert:
-Worse. Next you’ll be lecturing me on proper boat maintenance.
-Geralt:
-If we make it across, maybe.
-Lambert:
-What the—?
-Geralt:
-Probably just a log.
-Lambert:
-Or something that’s about to eat us.
-Geralt:
-(yawns)
-Wake me when it tries.
-Lambert:
-(laughs)
-Fine. Just don’t blame me if it swallows your boots.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cirilla: I barely escaped the Crones. And then there was the baron.
 Cirilla: You know he took me hunting? I killed a wild boar with my sword.
 Geralt: I heard.
@@ -477,80 +337,6 @@
 Cirilla: Mhm. Big as a bison and lumbering straight at me. And all I had was my sword. Had to manage.
 Geralt: Did just fine judging by how the baron's men remember it.
 Cirilla: Simple soldiers, the whole lot, but we got along splendidly. A shame I had to leave, flee, but I didn't want to bring the Wild Hunt down on them.
-</t>
-  </si>
-  <si>
-    <t>Ciri and Geralt talk about her meet with baron, haunting on boar and why she left.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Geralt:
-You gonna tell me why you left the baron’s place without a word?
-Ciri:
-(sighs)
-Figured you’d ask sooner or later.
-Geralt:
-Figured you’d dodge the question.
-Ciri:
-(grins)
-Guess we both figured right.
-Geralt:
-So?
-Ciri:
-(hesitates)
-The baron... he was decent, for the most part. Took me in, gave me food. Even tried to teach me how to use a crossbow.
-Geralt:
-A crossbow? You?
-Ciri:
-(chuckles)
-Yeah. Didn’t last long. Prefer a sword.
-Geralt:
-Smart girl.
-Ciri:
-We went hunting once. Boar. He wanted to impress me, I think. Show he wasn’t just some drunk bastard.
-Geralt:
-And?
-Ciri:
-It... almost worked. He was brave, I’ll give him that. Charged the boar like it was a wyvern. Almost got gored for it, too.
-Geralt:
-Sounds like him.
-Ciri:
-But after the hunt... he started talking. About his family. His wife, his daughter. How he’d messed up. I could see it—how guilt just... hung on him. Made me think of you.
-Geralt:
-Me?
-Ciri:
-How you always take the blame when things go wrong. Even when it’s not your fault.
-Geralt:
-(scoffs)
-Witcher habit. Comes with the job.
-Ciri:
-But it wasn’t like that with the baron. He did terrible things. Hurt people he claimed to love. And then... then he looked at me like I was some miracle. Like I could fix it all just by being there.
-Geralt:
-People see what they want. Sometimes more than what’s real.
-Ciri:
-Exactly. I couldn’t stand it. Couldn’t pretend everything was alright just because he wanted it to be. So I left.
-Geralt:
-Without saying goodbye?
-Ciri:
-Wasn’t sure I could. He’d start talking again—promising to change, to be better. And I... didn’t want to believe him.
-Geralt:
-Sometimes leaving’s the right choice. Doesn’t make it easy, though.
-Ciri:
-No. And... part of me wanted to stay. Thought maybe he could change. But then I remembered what you always say.
-Geralt:
-People don’t change just because they promise to.
-Ciri:
-(nods)
-Yeah. So I didn’t look back. Kept telling myself it was for the best.
-Geralt:
-You did what you had to. Proud of you.
-Ciri:
-(smiles faintly)
-Thanks.
-Geralt:
-Next time, leave a note. Or a sign. Makes finding you a bit easier.
-Ciri:
-(laughs)
-Can’t make it too easy for you, old man.
 </t>
   </si>
   <si>
@@ -602,9 +388,6 @@
 While the quest has ended at this point, the feast is still going on until you leave the area. If not spoken to previously, you talk to all the jarls around (Crach, Lugos, Donar and Holger Blackhand) while still there, you get an extra 100 XP earned based on the Story and Swords! difficulty level.</t>
   </si>
   <si>
-    <t>Warriors of Skellige talks on a feast but thei situation with Nilfgard. That is when Yennefer and Geralt are there.</t>
-  </si>
-  <si>
     <t>Guslar: Ask a service of the witcher, the pellar must. A witcherly service, that's to say…
 Geralt: What do you need, tell me.
 Guslar: A man who fears no evil, the pellar needs…
@@ -613,18 +396,6 @@
 Guslar: You'd not refuse, the pellar knew. The time's come to gather the folk.
 Guslar: Across the lake, we must journey - to Fyke Isle. There, in the circle of stones, we shall meet.
 Geralt: The sooner we resolve this, the better. Best do it tonight, at midnight.</t>
-  </si>
-  <si>
-    <t>Skellige Warrior 1: "To the waves that guard our shores! And may the Nilfgaardian dogs drown before they land!"
-Skellige Warrior 2: "Aye, but have you heard? They're claiming more lands down south. Like a bloody plague, spreading their black banners."
-Skellige Warrior 3: "Let them come. We'll break their bones on the cliffs and feed their corpses to the gulls."
-Skellige Warrior 4: "Easy to boast when they’re not here. But what if they do come? The mainland's trembling, says Hjalmar. Even Kaedwen’s bending the knee."
-Skellige Warrior 1: "Let the mainlanders cower. We’re Skelligers. No Nilfgaardian iron will tame our waves or our steel."
-Skellige Warrior 2: "True enough. But I heard tales from a trader. Says the Black Ones have ships now, bigger than ours, faster even."
-Skellige Warrior 3: "Ships or not, they can’t fight the winds. Or the storms we’ll call down on them."
-Skellige Warrior 4: "But what of our alliances? If the jarls don’t unite, we’ll be as scattered as broken mastwood."
-Skellige Warrior 1: "Then we fight as we’ve always done. For honor, for Skellige. Let the mainlanders bow, but never us."
-Skellige Warrior 2: "If only the gods would sink their fleet before it reaches our shores..."</t>
   </si>
   <si>
     <t>The Pellar was a rural holy man who lived near Blackbough. He sells a variety of crafting diagrams, runestones, and glyphs as well as alchemical ingredients and formulae at significantly lower prices. The Pellar was raised by an abusive father, who beat him and his mother, which led to the Pellar killing him. He spent his time helping people around the area, healing and offerering sage advice.</t>
@@ -641,25 +412,6 @@
 Return to the pellar's hut and tell him that you took care of the body. Doing so will finish the quest, earning you 50XP earned based on the Story and Swords! difficulty level + 50 , and unlocks a 10% discount with all merchants (regardless of type) in Velen and White Orchard. However, be aware that this also reduces the selling price of items.</t>
   </si>
   <si>
-    <t>The Pellar hires witcher for guarding ritual.</t>
-  </si>
-  <si>
-    <t>Pellar: "You... you’re the witcher, aye? The one who dealt with the wraiths in Blackbark Woods?"
-Witcher: "That’s me. What do you need?"
-Pellar: "Ritual. Needs guarding. Spirits... restless. Angry."
-Witcher: "What kind of ritual?"
-Pellar: "Cleansing. The land... tainted. Crops wither, cows birth stillborn calves. Must appease the spirits."
-Witcher: "Appeasing spirits usually means trouble. What’s causing it?"
-Pellar: "Curse. Old. Buried bones, bones that shouldn’t be disturbed. Folk did. Now the spirits lash out."
-Witcher: "And you want me to keep the angry spirits off your back while you fix it."
-Pellar: "Aye. It’s... dangerous. Spirits drawn to blood, to fear. You’ll be... distraction. Keep them at bay while I work."
-Witcher: "Dangerous for you, you mean. You plan on paying for this danger?"
-Pellar: "Forty crowns now. Forty more if we see dawn. Agreed?"
-Witcher: "Eighty total, huh? Fine. I’ll guard your bones, Pellar. When do we start?"
-Pellar: "Midnight. When the veil is thinnest. Meet by the old willow. And... bring your silver."
-Witcher: "Always do."</t>
-  </si>
-  <si>
     <t>If you know no fear and seek work, read this notice, for the call contained therein will be of great interest to you.
 Hans of Cidaris, soldier of fortune and veteran of many wars, hereby makes known the following: Being greatly concerned about the fate of the local peasantry, which suffers horribly from the attacks of some monster nesting in the forest near Oxenfurt, I have decided to grant a purse of Novigrad crowns to the man who slays this beast.
 Yet may it be known that any man who comes to me without a trophy shall receive no gold, but instead shall be tossed out on his arse so hard he shan't sit again till the end of his days.
@@ -674,15 +426,7 @@
 With the city's council demanding he either do the job or pay back the advancement he was given under threat of being imprisoned, he put up his own notice for someone more experienced to help him, albeit hiding the fact that it was his contract originally and he'd been paid well for it.</t>
   </si>
   <si>
-    <t>Hans of Cidaris want to give money evidance of slaying beast from near forest.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Write notice (from notice board) about: </t>
-  </si>
-  <si>
-    <t>Hans of Cidaris hereby declares his intention to reward any brave soul who can present evidence of slaying the beast terrorizing the outskirts of the nearby forest. The creature has caused great distress among the locals, and proof of its defeat will be generously compensated.
-Seek Hans at the Cidaris Inn for further details.
-May fortune favor the bold.</t>
   </si>
   <si>
     <t>Mates,
@@ -716,27 +460,12 @@
     <t>Widower</t>
   </si>
   <si>
-    <t>Rich old widower search for romantic partner</t>
-  </si>
-  <si>
     <t>Oxenfurt is a Redanian city located on the northern shore of the Pontar river and southeast of Novigrad. It is famous for its Academy, which is the largest in the Northern Kingdoms. It is about three hundred miles west of Tretogor.
 It is a bustling and bawdy haven for students, artists, scholars, and freethinkers. Here the young reign supreme (in spirit, if not always in fact), with a mug of something strong in hand as they blaze new trails in fashion and thought, confident that the rest of the world will soon follow.</t>
   </si>
   <si>
-    <t>Esteemed widower of advanced years, blessed with wealth and refined taste, seeks a mature and dignified lady for companionship. Preferably a widow or a lady of similar age, with grace, wisdom, and a kind heart. A landed background is welcome but not essential.
-If you possess a spirit as resilient as your beauty and seek pleasant company, please respond with a letter, including your full name, a valid return address, and a faithful likeness.
-Responses to be sent to: Poste Restante Gildorf, c/o "Romantic Soul"
-P.S. Ladies of elder races, especially halflings, need not apply.</t>
-  </si>
-  <si>
     <t xml:space="preserve">While searching for the witch Ciri had quarreled with, Geralt ran into an old friend – Keira Metz. The sorceress told the witcher about a masked mage. Ciri, it seemed, had taken shelter in his hideout. The witcher set off to find it, with Keira in tow.
 </t>
-  </si>
-  <si>
-    <t>Geralt was searching for the sorceress with whom Ciri had earlier quarreled. During his search, Geralt came across his old acquaintance, the sorceress Keira Metz, who informed him of the masked sorcerer in whose hideout Ciri had taken refuge. Geralt set out to find the magician's hideout, and Keira joined him.</t>
-  </si>
-  <si>
-    <t>Ciri encountered the Crones in the bog. The Crones took Ciri in but hesitated between eating her or handing her over to the Wild Hunt. Ciri escaped before they could decide. A spectral rider pursued her into the swamp. Geralt later arrived but lost her trail in the swamp.</t>
   </si>
   <si>
     <t>While in Crookback Bog, Ciri had happened on the Crones. The beastly sisters took her in, then wavered, unsure if they should eat her or surrender her to the Wild Hunt. Ciri escaped before they could decide. Pursued by a spectral rider, she had fled into the swamp – where Geralt lost her trail once more. He now needed a new lead.</t>
@@ -816,32 +545,6 @@
 The Wild Hunt clearly weren't there for a social visit as you will find a mass of graves. Just past the entrance to the village there's a fisherman who can be talked to, but he turns out to be quite useless. Eventually you will find priestesses performing a ritual honoring the fallen, Geralt suggests waiting, however Yennefer is not kind enough to wait and interrupts them. Like it or not you will inquire on what happened. Eventually the conversation will move on to Skjall and how he went to fight Morkvarg to regain his honor. If the quest In Wolf's Clothing was started but not completed, it will be updated now with info about the monster. If it was completed, Geralt will just mention the results of their meeting. Regardless it's time to go to Freya's Garden. Once you reach the garden the quest ends.</t>
   </si>
   <si>
-    <t xml:space="preserve">Talk between Yennefer, Geralt, Skellige Woman and two Priestesses. Geralt and Yenner asks about destruction of the village by Wild Hunt. </t>
-  </si>
-  <si>
-    <t>Yennefer: "How long since it happened?"
-Skellige Woman: "Three nights past. Came out of nowhere. Frost bit the ground, and the sky... it screamed."
-Geralt: "You saw them? The Wild Hunt?"
-Priestess 1: "Aye. Wraiths on black steeds, cloaked in ice and death. Tore through the village like a winter storm."
-Yennefer: "Did they take anyone?"
-Skellige Woman: "Hilda... and Olav’s boy. Gone. The rest... slaughtered. Like beasts."
-Priestess 2: "We found Hilda’s scarf near the cliffs. No tracks. Just... frost."
-Geralt: "Any survivors besides you?"
-Skellige Woman: "Few of us hid in the smokehouse. Didn’t dare move till dawn. When we crawled out... everything was ash. The fields, the houses... even the gods’ altar. Burned."
-Yennefer: "Did anyone see where they came from? Or where they went?"
-Priestess 1: "North. Toward the fjords. But they vanished with the morning light. Left only cold and ruin."
-Geralt: "Did you notice anything unusual before they came? Signs, omens?"
-Priestess 2: "The sacred oak cracked. Split clean in half. We thought it a bad omen, but... never this."
-Yennefer: "The Wild Hunt rarely strikes without reason. Did anyone here cross paths with strangers? Outsiders?"
-Skellige Woman: "A man passed through. Hooded, quiet. Carried a strange staff. Stayed one night, then gone by dawn."
-Geralt: "And you didn’t think to mention this before?"
-Priestess 1: "We thought him a simple druid. Seeking shelter. Didn’t know he’d bring death with him."
-Yennefer: (sighs) "Geralt, we need to find that druid. He might have drawn them here."
-Geralt: "Agreed. Which way did he go?"
-Priestess 2: "West, toward the whale graveyard. Said he needed bones for his rites."
-Yennefer: "If the Hunt’s tracking him, we’re already behind. Let’s move."</t>
-  </si>
-  <si>
     <t>Troll_2: Yum! Yum!
 Troll_3: Good 'uman, good soup.
 Troll_2: Salty?
@@ -878,28 +581,6 @@
   </si>
   <si>
     <t>Folan was a Skelliger warrior from Clan Tuirseach, and a companion of Hjalmar during the expedition to slay the ice giant Myrhyff.</t>
-  </si>
-  <si>
-    <t>Two Trolls talks about soup from human Folan (already in jar) which verbaly attacks them.</t>
-  </si>
-  <si>
-    <t>Folan: "You brainless rockheads! Let me out! I'll gut you both!"
-Troll 1: "Hah! Folan loud even in jar. Folan think scary."
-Troll 2: "Jar make Folan small. Small man, big mouth. Hurt troll ears."
-Folan: "When I get out, I'll hack your legs off! Use your skulls as mugs!"
-Troll 1: "Folan want soup, or be soup?"
-Troll 2: "Think Folan already soup. In jar. Just need heat."
-Folan: "I'll roast you both over a fire, you walking boulders!"
-Troll 1: "Folan roast trolls? Hah! Funny Folan."
-Troll 2: "Maybe roast Folan instead. Jar keep juice in. Good for soup."
-Troll 1: "Add roots? Make Folan soft. Folan too crunchy now."
-Folan: "Crunchy?! I'll show you crunchy when I break free!"
-Troll 2: "Hmmm... Folan noisy soup. Maybe add mushrooms. Make quiet."
-Troll 1: "Or smash jar first. Then soup. Less noise."
-Folan: "I'll have your heads on pikes! You'll regret this!"
-Troll 2: "Folan say many things. Trolls not listen. Soup not need talking."
-Troll 1: "Aye. Soup just need Folan. No mouth. More taste."
-Troll 2: "Heat pot. Folan stew soon. Good soup day."</t>
   </si>
   <si>
     <t>Regis: Yes, Geralt. It's me.
@@ -1043,9 +724,6 @@
     <t>Ibrahim Savi was an assistant professor at the Faculty of Natural History at the Oxenfurt Academy. He belonged to the research group mobilized by Professor Slavko Atimstein investigating the traces of witchers from three different schools. Ibrahim was assigned to research the School of the Bear.</t>
   </si>
   <si>
-    <t>Description of map to Castle Tuirseach by Ibrahim Savi.</t>
-  </si>
-  <si>
     <t>As Yennefer of Vengerberg told it, there had been a magic explosion in Skellige. Related to Ciri's reapperance, it had destroyed a vast swath of forest. Gerlat set out for the Isles to join the sorceress and seek further clues of Ciri's whereabouts. The druid Ermion, however, had no intention of letting Yennefer examine the woods. So Geralt and Yen sought out Jarl Crach an Craite, who helped break down the druid's resolve.</t>
   </si>
   <si>
@@ -1053,9 +731,6 @@
 Geralt later rendezvoused with Yennefer in Skellige during King Bran Tuirseach's funeral, where she explained that she suspected Ciri to be behind a cataclysm on the eastern end of Ard Skellig but Ermion, another of Ciri's tutors, refused to let her access the site, until they spoke with Crach an Craite. Afterwards, Yennefer and Geralt attended a wake at Kaer Trolde, where they stole the Mask of Uroboros, which possessed the ability to see the past events of the place it is viewed it. Upon arriving at the devastated area, they were confronted by Ermion, who warned them that it could only be used once and that using it will bring a cataclysm upon Skellige. As Geralt argued with Ermion, Yennefer went deeper into the devastated area and activated the mask, which caused a storm. Geralt ran to Yennefer and, using the mask's power, they found a place in the area where the elven mage had disintegrated a member of the Wild Hunt, then opened a portal and fled with Ciri. Ermion arrived soon after, and the two told him what they have found out. Ermion revealed to them that the Wild Hunt was recently seen on Hindarsfjall, so Geralt and Yennefer went there to investigate.
 Upon arriving to Hindarsfjall they went to the village of Lofoten, where the women were performing a ritual. Yennefer and Geralt interrupted them and asked about the Wild Hunt and Ciri. They were told that Ciri has been in the village, and that she was seen with a man they referred to as Craven. The two of them were in the stables right before the Wild Hunt arrived and attacked the village, killing many of its inhabitants. When asked about Craven, the women said that he went to the sacred garden near the village to defeat Morkvarg, some time after the incident, so Yennefer and Geralt went there to find him. In the garden, they found a body, and Yennefer decided to use necromancy to make it speak.
 The man's real name was Skjall. From what the body said, they learned that Ciri left with the elven mage on a boat as they were being chased by the Wild Hunt. Later on, Uma arrived on the same beach. After hearing the whole story, Yennefer forced the body to go back to its dead form. Yennefer's usage of necromancy drained all the magical power from the sacred garden, which the villagers of Lofoten didn't take lightly, and they blamed Yennefer and Geralt for not respecting their customs and beliefs. Still, Yennefer didn't care much about villagers' opinions, and she and Geralt ignored their claims. After leaving the garden, Yennefer asked Geralt to meet with her in Larvik, another village on Hindarsfjall, if he wanted to help her with something.</t>
-  </si>
-  <si>
-    <t>Magic Explosion in Skellige probabnly connected with Ciri. Gerlat joining Yennefer. Druid obstruction to examine forest. She seeks for help from jarl.</t>
   </si>
   <si>
     <t>On Hindarsfjall Geralt and Yen learned that Ciri had returned to the Isles. She'd rejoined her friend, the masked mage. They had boarded a boat and sailed off in an unknown direction. The boat had returned, one passenger on board – a creature as mindless as it was hideous.</t>
@@ -1070,9 +745,6 @@
   </si>
   <si>
     <t>Geralt found Ciri at last – on the Isle of Mists, where the elven mage had concealed her. There was no time to rejoice, for the Wild Hunt descended on them. They fled, Ciri teleporting them to Kaer Morhen, where their friends awaited. The Wild Hunt arrived at Kaer Morhen soon after. A great battle ensued, and the fortress' defenders might all have perished had Ciri not demonstrated her powers. So sudden and violent was her outburst that the Wild Hunt was forced to withdraw. The battle was won, the war had barely started.</t>
-  </si>
-  <si>
-    <t>Geralt found Ciri, they teleported to Kaer Morhen. Then the Wild Hunt attacked Kaer Morhen, but defenders won this battle.</t>
   </si>
   <si>
     <t xml:space="preserve">After you're all done and in front of the door, the dwarves will come out. However, they tell Geralt that Ciri is laying cold inside and the spirit has left her. A cutscene starts as they head for the boat and Geralt goes in to find her lifeless body. Devastated, he hugs her one last time, but as he does this, the firefly comes in and into Ciri, waking her and she embraces him back. You can then have a long conversation with her, recapping most of her story so far plus some tales of her travels between worlds. Feel free to talk about everything, despite being pushed for time by the Wild Hunt, everything is scripted.
@@ -1147,9 +819,6 @@
 Enter the Golden Sturgeon and head upstairs to talk with Corinne. She'll ask that you answer some questions truthfully to better help you. While there are a lot of options to give, you only need to answer one; the rest will just give background on the relationship between Geralt and Ciri. She'll then ask about Ciri's abilities, and you can again answer however you wish, before Corinne finally asks who you think Ciri would have gone to. Either choice will then go to a cutscene showing Dandelion, a swallow, and an explosion. Afterwards, Corinne will mention that the bard had inherited a brothel, The Rosemary and Thyme. </t>
   </si>
   <si>
-    <t>Triss direct Geralt to Corinne Tilly. She had a dream aboit Ciri and Dandelion meeting. Geralt decide to find Dandelion.</t>
-  </si>
-  <si>
     <t>The King of the Wild Hunt sailed aboard the Naglfar, a giant longship that traveled between worlds. As Ge'els had advised, the witcher set out to find the Sunstone – an artifact needed to draw Eredin into a trap.</t>
   </si>
   <si>
@@ -1157,132 +826,19 @@
 You then appear back in Novigrad, with Ciri around and Corinne Tilly to facilitate the dreaming. After witnessing the dream, Ge'els will tell you how to lure Eredin using the Sunstone and decides to withhold reinforcements for the Naglfar when the battle starts. Avallac'h then helps Ge'els return to Tir ná Lia and the quest ends after the Sage returns during a conversation with Ciri.</t>
   </si>
   <si>
-    <t>Eredin sailed on the Naglfar. Following Ge'els' advice, the witcher to find Sunstone.</t>
-  </si>
-  <si>
     <t>Context</t>
   </si>
   <si>
     <t>Write a book page about:</t>
   </si>
   <si>
-    <t>Metting a vampire called Regis, who saved his life. He shared with him some informations about vampires.</t>
-  </si>
-  <si>
-    <t>Geralt never expected to be saved by a vampire, least of all one as peculiar as Regis. The witcher awoke in a cave, wounds freshly bandaged, the metallic scent of blood lingering in the air. A figure sat nearby, silhouetted against the faint glow of a lantern—tall, composed, with an air of practiced calm.
-"You're awake," the figure said, his voice smooth as silk. "I was beginning to worry."
-Regis introduced himself, revealing his true nature without hesitation—a higher vampire, not bound by the sun or simple mortal cravings. Unlike the lesser beasts Geralt had hunted, Regis was eloquent and thoughtful, possessing a depth that defied his monstrous lineage.
-Curiosity overrode caution. As they shared a flask of herbal brew—Regis’s own concoction—the vampire spoke of his kind. He explained that not all vampires were bloodthirsty fiends. Higher vampires like himself lived far longer than humans could fathom, and most cherished knowledge, culture, and restraint. While lesser vampires could be driven by primal hunger, his kin could choose when and if they fed.
-Geralt listened, skeptical yet intrigued. Regis elaborated on the vampire society—ancient, complex, and largely detached from human affairs. Despite their power, higher vampires rarely interfered, content to watch from the shadows.
-When Geralt finally asked why Regis had saved him, the vampire smiled faintly. "Consider it repayment for centuries of my kind being misunderstood," he replied. "Besides, not all monsters are heartless, witcher."
-As dawn approached, Regis offered one final piece of advice: not every beast with fangs deserved the blade. Sometimes, understanding was the sharpest weapon of all.</t>
-  </si>
-  <si>
-    <t>Redanian administration letter of safe conduct  by Pontar</t>
-  </si>
-  <si>
-    <t>Redanian Royal Administration
-Pontar Border Authority
-Letter of Safe Conduct
-Issued under the authority of His Majesty, King Radovid V, Sovereign of Redania.
-Let it be known that the bearer of this document, ___________________, is granted safe and unrestricted passage across the Pontar River and through all border posts and crossings within the jurisdiction of the Redanian Crown.
-This safe conduct specifically permits travel for the purpose of ___________________, and the bearer shall not be hindered, detained, or subjected to undue inspection by Redanian guards or officials. Any attempt to contravene this decree will be considered a violation of royal authority and punishable under Redanian law.
-This letter remains valid until ___________________, and must be presented upon request at any border checkpoint or patrol.
-Issued at: ___________________
-Date: ___________________
-Signature: ___________________
-Seal of the Pontar Border Authority
-By command of His Royal Majesty, King Radovid V</t>
-  </si>
-  <si>
     <t xml:space="preserve">Write book page about: </t>
   </si>
   <si>
-    <t>Cretificate that allows to fight on Junior's arena as Zdenek</t>
-  </si>
-  <si>
     <t xml:space="preserve">Write </t>
   </si>
   <si>
-    <t>Official Certificate of Combat Entry
-Issued by the Arena Master, Oxenfurt Fighting Pits
-Authorization to Fight in Junior’s Arena
-This document certifies that the bearer, Zdenek, is officially recognized and granted permission to participate in all combat events held within Junior’s Arena.
-By the authority vested in the Arena Master and in accordance with the rules established by Cyprian Wiley, known as "Horson Junior", this certificate guarantees:
-Unrestricted Access: Zdenek may enter the arena grounds without hindrance.
-Right to Combat: Zdenek is permitted to engage in organized fights against designated opponents.
-Entitlement to Winnings: Upon victory, Zdenek will receive the agreed-upon share of the prize money.
-Protection from Interference: Any disruption to Zdenek’s participation will be treated as a breach of arena regulations.
-This certificate is valid until revoked by the Arena Master or Horson Junior himself. Zdenek is expected to adhere to the rules of combat and maintain the reputation of the arena.
-Issued on: ___________________
-Signature of Arena Master: ___________________
-Official Seal of Junior’s Arena</t>
-  </si>
-  <si>
-    <t>Dear Geralt,
-Priscilla has finally finished the script for the play, and your lines are ready. She put a lot of thought into making sure they sound just like you—short, blunt, and straight to the point. There’s even a bit of dry humor sprinkled in, just how you like it.
-Here are a few of your key lines to practice:
-(When asked about his purpose)
-"Hunting monsters. Not much else to it."
-(Responding to a noblewoman’s flirtation)
-"Pretty words. But I’ve heard prettier lies."
-(When questioned about destiny)
-"Never cared much for fate. Prefer a steel blade and a sharp mind."
-(Reflecting on past choices)
-"Regret’s a weight. Better to carry swords."
-Priscilla insists you focus on delivering them with that signature stoic charm. She says it’ll make the crowd love—or fear—you even more.
-Rehearsal’s tomorrow at dusk at the Rosemary and Thyme. Try not to scare the audience too much.
-– Dandelion</t>
-  </si>
-  <si>
-    <t>A note for Geralt with his lines for the play, which was written by Priscilla.</t>
-  </si>
-  <si>
-    <t>Write</t>
-  </si>
-  <si>
-    <t>Map to Castle Tuirseach
-Drawn and Annotated by Ibrahim Savi, Renowned Cartographer
-This meticulously crafted map guides the weary traveler to the ancient and formidable Castle Tuirseach, home to Clan Tuirseach, rulers of the unforgiving isle of An Skellig. The castle looms atop a jagged cliffside, defying both time and tempest.
-Directions:
-Begin your journey from Kaer Trolde Harbor. Follow the rugged coastal path northward, keeping the roar of the sea on your left.
-The path soon forks near the stone marker of Jarl Torold. Take the right path, ascending through the pine-clad slope.
-As the forest clears, the narrow ridge known as “Warrior’s Walk” will appear. Tread cautiously here, for the wind howls and the footing is treacherous.
-Once across, the ancient watchtower will come into view. Pass through its crumbling archway to enter the final ascent—a winding, uneven stair carved into the rock itself.
-At the summit, the great gates of Castle Tuirseach await, guarded by carved stone bears, the symbols of Clan Tuirseach’s strength and endurance.
-Traveler’s Notes:
-Beware the cliffside ravens—some say they are souls of the fallen warriors, watching over the path.
-The winds grow colder as you near the summit. Dress warmly, for the island spares none.
-Clan Tuirseach’s hospitality is as fierce as their loyalty—enter with respect, and leave with your head still on your shoulders.
-May this map serve you well, and may the winds favor your journey.
-– Ibrahim Savi, Cartographer of the Continent</t>
-  </si>
-  <si>
     <t xml:space="preserve">Write really short narrative (max 5 sentances) told by Dandelion, about this: </t>
-  </si>
-  <si>
-    <t>Ah, White Orchard—a sleepy village wrapped in the scent of apple blossoms, where peace seems to linger despite the war creeping closer. It was there that Geralt, ever the reluctant hero, arrived searching for Yennefer. Instead, he found trouble—griffin attacks, whispers of Nilfgaard, and villagers caught between fear and fate. The White Wolf, though focused on his quest, couldn’t help but intervene, his blade swift and his heart—despite what he’d claim—not entirely untouched. Little did he know, his journey had only just begun.</t>
-  </si>
-  <si>
-    <t>Ah, what a moment that was! Geralt, weary from the road and soaked in griffin blood, finally caught wind of Yennefer’s whereabouts. A simple innkeeper’s whisper—just a name and a direction—but it was enough to set the White Wolf’s heart racing. Hope sparked in his tired eyes, and without a second thought, he was off, chasing fate once more. Love, after all, makes even a witcher reckless.</t>
-  </si>
-  <si>
-    <t>Ah, destiny's threads do love to tangle! While searching for the sorceress who’d quarreled with Ciri, Geralt stumbled upon none other than Keira Metz—charming, cunning, and as unpredictable as ever. She spoke of a masked mage and his mysterious hideout, where Ciri had sought refuge. Sensing a trail worth following, Geralt set off, with Keira—ever curious—insisting on joining. Together, they ventured into the unknown, guided by secrets and shadows.</t>
-  </si>
-  <si>
-    <t>Ah, Ciri and the Crones—now there’s a tale that sends shivers down my spine! The Crones of Crookback Bog took her in, their wicked minds torn between devouring the girl or selling her soul to the Wild Hunt. But Ciri, ever the clever fox, slipped through their gnarly fingers before they could make up their minds. A spectral rider gave chase through the mist-laden swamp, but the girl vanished like a wisp of fog. When Geralt arrived, all that remained were hoof prints and the lingering scent of fear.</t>
-  </si>
-  <si>
-    <t>Ah, fate’s a crafty weaver! Triss pointed Geralt toward Corinne Tilly, a gifted oneiromancer with dreams as vivid as life itself. Turns out, she saw Ciri meeting yours truly—imagine that! Geralt, of course, decided that if anyone knew where our ashen-haired fugitive had gone, it’d be me. And so, the chase led him straight to my charming, if slightly chaotic, doorstep.</t>
-  </si>
-  <si>
-    <t>Ah, Skellige—land of storms and stubborn druids! A mighty magical blast rocked the isles, and Yennefer was convinced it had Ciri’s name written all over it. Geralt joined her, naturally, but the druids weren’t exactly rolling out the welcome wagon. Stubborn as ever, Yennefer decided to cut through the red tape by appealing to a jarl for permission. After all, when magic’s afoot, diplomacy often needs a touch of force!</t>
-  </si>
-  <si>
-    <t>Ah, what a reunion that was! Geralt finally found Ciri, and together they whisked away to Kaer Morhen, that old bastion of witcher lore. But peace was short-lived—the Wild Hunt came crashing down like a winter storm. The battle was fierce, blades flashing and magic crackling, but against all odds, the defenders stood firm. Kaer Morhen held its ground, and the Wild Hunt slunk away, licking its wounds.</t>
-  </si>
-  <si>
-    <t>Ah, the Naglfar—Eredin’s dreaded ghost ship, cutting through worlds like a blade through silk! That wily elf Ge’els tipped Geralt off, suggesting that the key to stopping the Wild Hunt lay in the legendary Sunstone. With it, they could summon Eredin from his spectral voyage and force a final clash. Of course, finding an ancient elven artifact isn’t exactly a stroll through the woods. But when has Geralt ever shied away from a challenge?</t>
   </si>
   <si>
     <t>Skellige sagas brim with praise for war chiefs and warrior-braves of ages past, yet the saga of Crach, jarl of the Clan an Craite and lord of Kaer Trolde, will outshine them all. It will sing of his strength, his courage, his wisdom, his generosity, his loyalty to friends and his relentless pursuit of his foes.
@@ -1496,9 +1052,6 @@
 Peter: "You have my word, witcher. Kill the beast, and I’ll tell you all I know."</t>
   </si>
   <si>
-    <t>Dialogue between Cerys and Udalryk, after Cerys' plan. She tries to convince him that she would never harm his child and explains her plan.</t>
-  </si>
-  <si>
     <t>hmm</t>
   </si>
   <si>
@@ -1554,12 +1107,395 @@
 -    List of facts that need to be contained: ["Quote about Sylvan"]
 -    Thematic: Sylvan</t>
   </si>
+  <si>
+    <r>
+      <t>Udalryk an Brokvar</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t> was the jarl of Clan Brokvar from Spikeroog in Skellige Islands. dalryk was born as the eldest son of the Jarl of Spikeroog though was soon joined by a younger brother, Aki. While the two got along well enough, their father appeared to favor Aki, going as far as bestowing the family's heirloom sword Brokvar on the younger son rather than following Skelligan custom and giving it to the firstborn son, which was considered to be a serious insult to Udalryk. Enraged at this, Udalryk publicly questioned his father's decision, breaking one of Skellige's sacred laws in doing so, and was subsequently punished by being chained to a pile in the sea for three days. Afterwards, to try and make amends, he and Aki went out on a sailing trip near Ulula's Needle when a storm broke out and Aki fell overboard. Udalryk, who had his hands full with the sails, didn't hear his brother's cry for help until it was too late and Aki drowned.
+Having failed to save his brother, Udalryk was overcome with immense guilt and sometime afterwards began to hear voices in his sleep that claimed they were messengers from the gods. These voices plagued Udalryk with strange visions and commanded he harm himself as a sacrifice to the gods, like cutting himself deep enough to leave scars, though he viewed this as a gift to hear from the gods so directly.
+Eventually he became the jarl of Clan Brokvar and by 1272 had his own son, who he named Aki in honor of his deceased brother.</t>
+    </r>
+  </si>
+  <si>
+    <t>Cerys: "Udalryk... you need to listen. I’ve spent days sifting through the old sagas, talking to your people. I know what haunts you — it’s not the gods. It’s your guilt. Your fear."
+Udalryk: "You know nothing of what I’ve lost. Of what I’ve done. That… thing, it watches me, it whispers—"
+Cerys: "Then let me silence it. I’ve a plan. We draw it out, trap it. Break the curse once and for all. But I need your trust."
+Udalryk: "And my child? This plan of yours—"
+Cerys: "I swear on Freya’s name — I would never harm your child. I’ll stake my claim to the throne on that. I want to help, not destroy what little peace you have left."
+Udalryk: "Then may the gods be with us both…"</t>
+  </si>
+  <si>
+    <t>Write text to game Witcher 3: Wild Hunt. Your guideline:
+Creators – Cerys an Craite, Udalryk an Brokvar
+Type of text – Dialogue
+Length – Between 120-180 words
+Content:
+- List of facts that need to be contained: [“Cerys explains her plan”, “Cerys convince that she would never hurt Udalryk baby”]
+- Participants - Cerys an Craite, Udalryk an Brokvar</t>
+  </si>
+  <si>
+    <t>Geralt: That your boat?
+Lambert: It floats. Most of the time.
+Geralt: Reassuring.
+Lambert: You wanna swim across, be my guest. Personally, I like dry boots and not being eaten by drowners halfway there.
+Geralt: Fine. But if this thing sinks halfway through, I’m blaming you.
+Lambert: That’s fair. I blame myself every time I use it.
+Geralt: Thought about fixing it?
+Lambert: Thought about fixing you, too. We both keep going, don’t we?
+Geralt: Point taken.</t>
+  </si>
+  <si>
+    <t>Geralt: You alright? When I saw you on the Isle... thought I'd lost you for good.
+Ciri: I'm fine now. Just... needed time. Everything felt heavy, like the mists themselves.
+Geralt: Heard you went to see the Bloody Baron. That true?
+Ciri: Yeah. Thought he might help. And... he did, in his own way. Let me rest, gave me food.
+Geralt: Man's got more sides than a dice.
+Ciri: He was broken, Geralt. Talked about his daughter, his wife... Guess I reminded him of someone.
+Geralt: Why'd you leave?
+Ciri: There was a hunt — a boar, not far from Crow's Perch. I went with his men. It felt good at first. Like I belonged somewhere.
+Geralt: And then?
+Ciri: One of the hounds found a grave. Shallow, fresh. Something about it chilled me. I couldn’t stay. Couldn’t pretend everything was fine.
+Geralt: You did the right thing.
+Ciri: Doesn’t make it easier. But thanks. For finding me. For not giving up.</t>
+  </si>
+  <si>
+    <t>Skellige Warrior 1: Feasts ain't what they used to be. Meat's fine, mead flows, but there's a shadow over it all.
+Skellige Warrior 2: Aye, hard to raise a horn when Nilfgaard breathes down our necks. Their black sails blot out the sea like crows before a storm.
+Skellige Warrior 3: Let 'em come. We’ve got axes enough and blood to spare. Skellige bends the knee to no southern king.
+Skellige Warrior 1: Brave words, but even brave men die. You hear what happened in Cintra? Burned to ash while nobles danced.
+Skellige Warrior 2: Still... tonight, we drink. For what’s left of peace.
+Skellige Warrior 3: And for the witcher and the sorceress. Never thought I’d see a White Wolf stalk our halls with Yennefer of Vengerberg at his side.
+Skellige Warrior 1: Strange days. Maybe that means the gods haven’t turned their backs on us after all.
+Skellige Warrior 2: Or they’re just sharpening their blades. Either way — drink now. Fight later.</t>
+  </si>
+  <si>
+    <t>Geralt: You wanted to see me?
+Guslar: Aye, witcher. The spirits grow restless, old voices stirring in the dark. I must perform a rite to quiet them.
+Geralt: And you need someone to make sure nothing interrupts.
+Guslar: Sharp, you are. The ritual’s no simple chant and dance — it calls to those long buried. Not all who answer are kindly.
+Geralt: Where?
+Guslar: Fyke Isle. The land’s soaked in sorrow, but the veil is thin there. It must be done under moon’s gaze.
+Geralt: You’re either brave or mad. Alright. I’ll keep you breathing.
+Guslar: For coin, of course. And perhaps a blessing or two from the old ones — if they’re in the mood.
+Geralt: I’ll take coin. Blessings tend to come with curses.</t>
+  </si>
+  <si>
+    <t>Geralt: This village—burned to the ground. No signs of resistance. Just death.
+Yennefer: The Wild Hunt passed through here. We need to know what they wanted.
+Skellige Priestess: You’ve come seeking truth among ashes. Speak with Ragna. She saw what the gods should never show.
+Geralt: Ragna?
+Skellige Woman: Aye… I saw them. Came like a storm with no sky. Frost clung to their cloaks, blades like ice. They rode through like wraiths.
+Yennefer: Did they speak? Do anything strange?
+Skellige Woman: Not speak… howl. One word again and again. Don’t know its meaning. But they searched every home. Tore open cellars, lifted floorboards.
+Geralt: Looking for someone.
+Skellige Priestess: The earth remembers their chill. The land won’t warm again soon.
+Yennefer: Did they take anyone? A child, perhaps?
+Skellige Woman: No. Only left bodies behind. But their eyes… they were hunting. Not raiding.
+Geralt: Then we’re on the right trail. Let’s not waste it.</t>
+  </si>
+  <si>
+    <t>Troll 1: Mmm… human soup soon. Smell good, this one. Little hairy, little loud.
+Troll 2: Jar nice. Keep meat fresh. Maybe add roots. Maybe mushrooms.
+Folan: You stinking rock-brains! Let me out! I’ll skin you both and make boots from your hides!
+Troll 1: He spicy. Spicy make soup better.
+Troll 2: But talk too much. Maybe bash head first? Bash, then boil?
+Folan: You try it, and I swear by Skellige’s gods, I’ll haunt your dreams!
+Troll 1: Mmm… haunted soup. Never had that.</t>
+  </si>
+  <si>
+    <t>Write text to game Witcher 3: Wild Hunt. Your guideline:
+Creators – Two Trolls, Folan
+Type of text – Dialogue
+Length – Between 40-100 words
+Content
+-	List of facts that need to be contained: [“Two Trolls talks about soup from human Folan” , ”Folan is already in jar”, “Folan verbally attacks trolls”]
+-	Participants: Two Trolls, Folan</t>
+  </si>
+  <si>
+    <t>Write text to game Witcher 3: Wild Hunt. Your guideline:
+Creators – Geralt of Rivia, Guslar
+Type of text – Dialogue
+Length – Between 100-140 words
+Content
+-	List of facts that need to be contained: [“The Pellar hires witcher for guarding ritual”, “Ritual occurs on Fyke Isle”]
+-	Participants: Geralt of Rivia, Guslar</t>
+  </si>
+  <si>
+    <t>Write text to game Witcher 3: Wild Hunt. Your guideline:
+Creators – Geralt of Rivia, Skellige Priestesses, Skellige Woman Witness Of Attack, Yennefer of Vengerberg
+Type of text – Dialogue
+Length – Between 120-180 words
+Content
+-	List of facts that need to be contained: [“Geralt and Yenner asks about destruction of the village by Wild Hunt”, “Skellige Woman speaks about slaughter”]
+-	Participants: Geralt of Rivia, Skellige Priestesses, Skellige Woman, Yennefer of Vengerberg</t>
+  </si>
+  <si>
+    <t>Write text to game Witcher 3: Wild Hunt. Your guideline:
+Creators – Skellige Warriors
+Type of text – Dialogue
+Length – Between 120-180 words
+Content
+-	List of facts that need to be contained: [“Warriors of Skellige talks on a feast but the situation with Nilfgard”, “This is happening on the event with Geralt and Yennefer”]
+-	Participants: Skellige Warriors</t>
+  </si>
+  <si>
+    <t>Write text to game Witcher 3: Wild Hunt. Your guideline:
+Creators – Geralt of Rivia, Ciri
+Type of text – Dialogue
+Length – Between 120-180 words
+Content
+-	List of facts that need to be contained: [“Ciri and Geralt meet on Isle of Mists”, “They talk about her meeting with Baron”, “She includes haunting on boar and why she left”]
+-	Participants: Geralt of Rivia, Ciri</t>
+  </si>
+  <si>
+    <t>Write text to game Witcher 3: Wild Hunt. Your guideline:
+Creators – Geralt of Rivia, Lambert
+Type of text – Dialogue
+Length – Between 120-180 words
+Content
+-	List of facts that need to be contained: [“They talking about going across the lake”, “Lambert have boat but it is not in great state”, “Dialogue continue on boat”]
+-	Participants: Geralt of Rivia, Lambert
+-	Tone: Chill, old friends</t>
+  </si>
+  <si>
+    <t>Excerpt from "A Treatise on Necrophage Behavior" by Master Alvarin of Oxenfurt
+Among the more commonly encountered necrophages, ghouls and alghouls represent a unique blend of opportunistic scavenging and territorial aggression. While both species are drawn to mass graves and battlefields, their behaviors and social structures differ notably.
+Ghouls tend to operate in loose packs, driven by scent and hunger rather than strategy. They fear fire and react violently to sudden movement or noise, making them particularly dangerous to the untrained. Curiously, they avoid corpses that show signs of disease — a primitive form of instinctual preservation, perhaps.
+Alghouls, on the other hand, exhibit greater resilience and a heightened sense of self-preservation. Upon sensing danger, an alghoul will raise the thick spines along its back, a defensive posture often mistaken for aggression. Unlike ghouls, alghouls rarely flee; they fight viciously, often coordinating with nearby ghouls in sudden, brutal attacks.
+Both creatures are vulnerable to necrophage oil, though silver remains the most reliable solution when scholarly theory fails — as it often does.</t>
+  </si>
+  <si>
+    <t>Write text to game Witcher 3: Wild Hunt. Your guideline: 
+Creators: Scientist
+Type of text: Book page
+Length: between 125-175 words 
+Content: 
+-    Thematic: Ghouls and Alghouls</t>
+  </si>
+  <si>
+    <t>Last Words of a Grateful Soul
+Penned by Handrik of Dillingen
+I write these lines with hands worn thin and breath shallow — not from injury, but from time, which steals more cruelly than any sword. Many decades ago, I wandered the Yaruga wounded and lost, a foolish boy thinking himself a man. That night, death surely waited. But he did not come.
+Instead, a figure stepped from the mist. Pale, eyes like molten gold — not cruel, but ancient. He called himself Regis. A vampire, yes, but nothing like the tales. No beast, no monster. He fed not on fear, but on knowledge, compassion even. He gave me water, cleaned my wounds with herbs I had no name for, and stayed by my fire till dawn.
+We spoke of his kind. He told me vampires are many — ekimmaras, fleders, higher ones like himself. Some wild, some wise. He’d lived for centuries, yet carried his immortality like a burden.
+He saved my life. And now, as mine ends, I wonder if he still walks this world — and if he remembers the boy by the river.</t>
+  </si>
+  <si>
+    <t>Write text to game Witcher 3: Wild Hunt. Your guideline: 
+Creators: Written by dying of age old man
+Type of text: Book page
+Length: between 125-175 words 
+Content: 
+-    List of facts that need to be contained: [“Text tells about meeting a vampire called Regis, who is saving man life”, “Regis shared with him some informations about vampires.”]
+- Participants:  Regis, younger writer</t>
+  </si>
+  <si>
+    <t>Redanian Letter of Safe Conduct
+By order of His Royal Majesty Radovid V the Stern
+Let it be known that the bearer of this letter is granted safe passage through all Redanian-held territories along the Pontar, including but not limited to river crossings, outposts, and border garrisons.
+No toll, tax, or detainment shall be imposed. Interference with the bearer shall be punishable under Royal Decree 743-B.
+Signed and sealed in Oxenfurt,
+Chancellor Hieronim Rütten, Redanian Bureau of Border Affairs</t>
+  </si>
+  <si>
+    <t>Write text to game Witcher 3: Wild Hunt. Your guideline: 
+Creators: Made by Redanian Administration
+Type of text: letter of safe conduct  
+Length: between 20-100 words 
+Content: 
+-    Thematic: Redanian administration letter of safe conduct  by Pontar</t>
+  </si>
+  <si>
+    <t>Let it be known across the land that a grievous beast has taken to haunting the woods east of Cidaris, near the old stone circle. Livestock vanish without trace, travelers return torn or not at all, and strange howls echo through the trees at dusk.
+Hans of Cidaris, sworn sword to His Grace Duke Rotwald, hereby offers fair coin to any soul brave (or foolish) enough to rid the region of this menace. The reward shall be granted only upon presentation of tangible proof of the creature’s death — be it fang, claw, hide, or other unmistakable token.
+Those seeking to claim the bounty should make their way to the guard post at the southern gate of Cidaris, where Marshal Tebern will register names and accept evidence.
+May the gods shield you, and may your blade strike true.
+— Hans of Cidaris</t>
+  </si>
+  <si>
+    <t>To the Ladies of Oxenfurt and Beyond
+— A Heart Still Beating
+Hung with care upon the notice board in Oxenfurt:
+I, Ewald of Vellin, once a merchant of linens and now a widower of means and quiet evenings, seek companionship in my twilight years. My manor rests on the hill outside the city, with warm hearths, well-tended vines, and no shortage of coin or books to pass the time.
+I do not ask for youth, nor promises. Only that you share a fondness for conversation, stew seasoned with rosemary, and long walks beneath the moon.
+Let no one scoff — though my beard is grey and my joints less lively, my heart remains sound and open.
+Those with sincere interest may leave word at the Crippled Kate’s, under the name “Ewald the Patient.”
+Let us not go to the grave alone, when laughter still lingers in the air.
+— Ewald of Vellin, widower and romantic</t>
+  </si>
+  <si>
+    <t>Write text to game Witcher 3: Wild Hunt. Your guideline: 
+Creators: Widower
+Type of text: announcement
+Length: between 125-175 words 
+Content: 
+-    Thematic: Rich old widower search for romantic partner
+-    List of facts: [“Announcement hang in Oxenfurt”]</t>
+  </si>
+  <si>
+    <t>Write text to game Witcher 3: Wild Hunt. Your guideline: 
+Creators: Hans of Cidaris
+Type of text: announcement
+Length: between 125-175 words 
+Content: 
+-    Thematic: Hans of Cidaris want to give money for evidence of slaying beast from near forest.</t>
+  </si>
+  <si>
+    <t>Bearer: Zdenek
+Is hereby granted right to fight in Junior’s Arena. No guards shall bar entry. Winnings subject to the House's take.
+— Authorized by Order of Whoreson Junior</t>
+  </si>
+  <si>
+    <t>Write text to game Witcher 3: Wild Hunt. Your guideline: 
+Creators: Junior's arena 
+Type of text: cretificate
+Length: between 15-40 words 
+Content: 
+-    Thematic: Cretificate that allows to fight on Junior's arena as Zdenek</t>
+  </si>
+  <si>
+    <t>Geralt – Your Lines
+Don’t forget these, or Dudu will upstage you!
+Act II, Scene III
+“You foul beast, thy reign of terror ends now!”
+pause for dramatic effect
+“I draw silver not for coin, but for justice!”
+Act III, Scene I
+“I have walked through fire, storm, and shadow — and I fear no phantom born of lies!”
+Break a leg, witcher. And please, try not to mumble.
+— Priscilla</t>
+  </si>
+  <si>
+    <t>Write text to game Witcher 3: Wild Hunt. Your guideline: 
+Creators: Priscilla
+Type of text: note
+Length: between 60-100 words 
+Content: 
+-    Thematic: A note for Geralt with his lines for the play, which was written by Priscilla.</t>
+  </si>
+  <si>
+    <t>The map charts the cliffs of An Skellig, leading to Castle Tuirseach — marked with an ancient bear sigil etched beneath moss. I discovered it by moonlight… just before I heard footsteps not my own. Something still follows me. It does not tire. If you find this, beware the path and the shadow behind you.</t>
+  </si>
+  <si>
+    <t>Write text to game Witcher 3: Wild Hunt. Your guideline: 
+Creators: Ibrahim Savi
+Type of text: Description of map
+Length: between 35-65 words 
+Content: 
+-    Thematic: Description of map to Castle Tuirseach
+-   List of facts that need to be contained: [“Something is still following him”, “Castle Tuirseach
+has bear symbol which he discovered”, ]</t>
+  </si>
+  <si>
+    <t>Ah, White Orchard — quiet, sun-dappled, and smelling faintly of apple blossoms and old secrets. It was here our tale began anew, with Geralt chasing shadows of war and Yennefer chasing him. As always, destiny had other plans — sharp, tangled, and utterly inconvenient.</t>
+  </si>
+  <si>
+    <t>Write text to game Witcher 3: Wild Hunt. Your guideline:
+Creators: Dandelion
+Type of text: Narration
+Length: between 30-50 words
+ Content:
+-     Participants: Geralt, Yennefer
+ -    Thematic: An introduction to the story set in White Orchard</t>
+  </si>
+  <si>
+    <t>Near Vizima’s gilded gates, where politics rot faster than corpses, Yennefer lingered — cloaked in secrets and lilac. Geralt, ever the moth to her flame, followed close behind. Love or fate? With those two, it’s always both.</t>
+  </si>
+  <si>
+    <t>Write text to game Witcher 3: Wild Hunt. Your guideline:
+Creators: Dandelion
+Type of text: Narration
+Length: between 20-50 words
+ Content:
+-     Participants: Geralt, Yennefer
+ -    List of facts that need to be contained: [“Yen is nearby Vizima”]</t>
+  </si>
+  <si>
+    <t>Ah, Geralt — always chasing trouble, or in this case, a sorceress Ciri had quarreled with. While sniffing out arcane scents and old grudges, he stumbled upon Keira Metz, an enchantress with a talent for meddling. She spoke of a masked sorcerer and Ciri’s brief refuge in his hideout. Without delay, Geralt set off to find it — and Keira, naturally, insisted on tagging along.</t>
+  </si>
+  <si>
+    <t>Write text to game Witcher 3: Wild Hunt. Your guideline:
+Creators: Dandelion
+Type of text: Narration
+Length: between 40-70 words
+ Content:
+-     Participants: Geralt, Ciri, Keria Metz
+ -    List of facts that need to be contained: [“Geralt was searching for the sorceress with whom Ciri had earlier quarreled”, “During his search, Geralt came across his old acquaintance, the sorceress Keira Metz, who informed him of the masked sorcerer in whose hideout Ciri had taken refuge”, “Geralt set out to find the magician's hideout, and Keira joined him.”]</t>
+  </si>
+  <si>
+    <t>Write text to game Witcher 3: Wild Hunt. Your guideline:
+Creators: Dandelion
+Type of text: Narration
+Length: between 50-80 words
+ Content:
+-     Participants: Geralt, Ciri, The Crones, Wild Hunt
+ -    List of facts that need to be contained: [“Ciri encountered the Crones in the bog.”, “The Crones took Ciri in but hesitated between eating her or handing her over to the Wild Hunt.”, “Ciri escaped before they could decide”, “A spectral rider pursued her into the swamp”, “Geralt later arrived but lost her trail in the swamp”]</t>
+  </si>
+  <si>
+    <t>Ciri’s path led her deep into the bog, where fate — ever cruel — brought her before the Crones. They took her in, torn between devouring her or delivering her to the Wild Hunt. Before their twisted minds could settle, Ciri escaped. A spectral rider gave chase, vanishing into the mist behind her. By the time Geralt arrived, all that remained was the swamp’s silence… and a trail gone cold.</t>
+  </si>
+  <si>
+    <t>Triss, ever resourceful, pointed Geralt toward Corinne Tilly — a dreamer known for visions that danced dangerously close to truth. Corinne spoke of a dream: Ciri, fierce and hurried, meeting none other than Dandelion. Geralt, connecting the pieces with witcherly instinct, wasted no time. If Dandelion had seen Ciri, he’d know where she’d gone. And so, the search for our charming bard began. Gods help us all.</t>
+  </si>
+  <si>
+    <t>Write text to game Witcher 3: Wild Hunt. Your guideline:
+Creators: Dandelion
+Type of text: Narration
+Length: between 50-80 words
+ Content:
+-     Participants: Geralt, Dandelion, Triss, Corinne Tilly
+ -    List of facts that need to be contained: [“Triss direct Geralt to Corinne Tilly”, “She had a dream about Ciri and Dandelion meeting”, “Geralt decide to find Dandelion.”]</t>
+  </si>
+  <si>
+    <t>When a surge of wild magic shook the isles of Skellige, all signs pointed to one source — Ciri. Yennefer, sharp-eyed and sharper-tongued, set out to investigate the blast, but met resistance from the ever-suspicious druid Ermion, who barred her from the forest. Sensing more than moss and roots at play, she turned to Jarl Crach an Craite for aid. Meanwhile, Geralt, drawn by both storm and sorceress, arrived to join her in uncovering the truth.</t>
+  </si>
+  <si>
+    <t>Write text to game Witcher 3: Wild Hunt. Your guideline:
+Creators: Dandelion
+Type of text: Narration
+Length: between 60-90 words
+ Content:
+-     Participants: Geralt, Yennefer, Ciri, Crach an Craite, druid Ermion
+ -    List of facts that need to be contained: [“Magic Explosion in Skellige probably connected with Ciri”, “Geralt is joining Yennefer”, “Druid obstruction to examine forest. She seeks for help from jarl”]</t>
+  </si>
+  <si>
+    <t>At long last, Geralt found Ciri — weary, battle-worn, but alive. Their reunion, though brief, brought little peace. With danger snapping at their heels, they teleported to Kaer Morhen, the ancient keep of the witchers. But safety proved short-lived. The Wild Hunt, relentless as ever, tracked them down and launched a brutal assault. Steel clashed, spells crackled, and blood soaked the snow. Yet the defenders — witchers, sorceresses, and allies alike — stood their ground. Against all odds, they won the battle… but the war was far from over.</t>
+  </si>
+  <si>
+    <t>Write text to game Witcher 3: Wild Hunt. Your guideline:
+Creators: Dandelion
+Type of text: Narration
+Length: between 80-120 words
+ Content:
+-     Participants: Geralt, Ciri, Wild Hunt
+ -    List of facts that need to be contained: [“Geralt found Ciri, they teleported to Kaer Morhen”, “Then the Wild Hunt attacked Kaer Morhen, but defenders won this battle”]</t>
+  </si>
+  <si>
+    <t>Eredin, aboard the dreaded Naglfar, drew ever closer. But not all among the Aen Elle stood with him. Heeding Ge’els’ counsel, Geralt set out in search of the legendary Sunstone — the key to luring the Wild Hunt’s king into battle on his own terms.</t>
+  </si>
+  <si>
+    <t>Write text to game Witcher 3: Wild Hunt. Your guideline:
+Creators: Dandelion
+Type of text: Narration
+Length: between 30-50 words
+ Content:
+-     Participants: Geralt, Eredin, Ge'els
+ -    List of facts that need to be contained: [“Eredin sailed on the Naglfar”, “Following Ge'els' advice, the witcher to find Sunstone”]</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1607,19 +1543,6 @@
       <charset val="238"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="238"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="238"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="Calibri"/>
@@ -1627,8 +1550,76 @@
       <charset val="238"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="26"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="26"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="28"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="238"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="238"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="238"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="238"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1638,6 +1629,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1652,9 +1649,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1672,22 +1669,32 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Dobry" xfId="1" builtinId="26"/>
@@ -1975,63 +1982,62 @@
   <dimension ref="B1:G7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="2"/>
-    <col min="2" max="2" width="58.85546875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="54.85546875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="40.42578125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="43.28515625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="42" style="2" customWidth="1"/>
-    <col min="7" max="7" width="46.85546875" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="9.140625" style="12"/>
+    <col min="2" max="2" width="58.85546875" style="12" customWidth="1"/>
+    <col min="3" max="3" width="54.85546875" style="12" customWidth="1"/>
+    <col min="4" max="4" width="40.42578125" style="12" customWidth="1"/>
+    <col min="5" max="5" width="43.28515625" style="12" customWidth="1"/>
+    <col min="6" max="6" width="42" style="12" customWidth="1"/>
+    <col min="7" max="7" width="46.85546875" style="12" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B1" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D1" s="7" t="s">
+      <c r="B1" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>28</v>
+      <c r="E1" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="D2" s="5" t="s">
+      <c r="C2" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="D2" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="G2" s="5" t="s">
+      <c r="E2" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="G2" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" spans="2:7" ht="173.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="3"/>
-      <c r="C3"/>
-      <c r="D3" s="5" t="s">
+      <c r="B3" s="16"/>
+      <c r="D3" s="14" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E7" s="2" t="s">
-        <v>175</v>
+      <c r="E7" s="12" t="s">
+        <v>127</v>
       </c>
     </row>
   </sheetData>
@@ -2047,58 +2053,58 @@
   <dimension ref="B1:G3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="2"/>
-    <col min="2" max="2" width="58.85546875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="54.85546875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="40.42578125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="43.28515625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="42" style="2" customWidth="1"/>
-    <col min="7" max="7" width="77.85546875" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="9.140625" style="12"/>
+    <col min="2" max="2" width="58.85546875" style="12" customWidth="1"/>
+    <col min="3" max="3" width="54.85546875" style="12" customWidth="1"/>
+    <col min="4" max="4" width="40.42578125" style="12" customWidth="1"/>
+    <col min="5" max="5" width="43.28515625" style="12" customWidth="1"/>
+    <col min="6" max="6" width="42" style="12" customWidth="1"/>
+    <col min="7" max="7" width="77.85546875" style="12" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B1" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D1" s="7" t="s">
+      <c r="B1" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="4" t="s">
+      <c r="E1" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="G2" s="14"/>
+    </row>
+    <row r="3" spans="2:7" ht="173.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="16"/>
+      <c r="C3" s="18" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="G2" s="5"/>
-    </row>
-    <row r="3" spans="2:7" ht="173.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="3"/>
-      <c r="C3" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>14</v>
+      <c r="D3" s="14" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -2111,54 +2117,54 @@
   <dimension ref="B1:G3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="2"/>
-    <col min="2" max="2" width="58.85546875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="54.85546875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="40.42578125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="43.28515625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="42" style="2" customWidth="1"/>
-    <col min="7" max="7" width="77.85546875" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="9.140625" style="12"/>
+    <col min="2" max="2" width="58.85546875" style="12" customWidth="1"/>
+    <col min="3" max="3" width="54.85546875" style="12" customWidth="1"/>
+    <col min="4" max="4" width="40.42578125" style="12" customWidth="1"/>
+    <col min="5" max="5" width="43.28515625" style="12" customWidth="1"/>
+    <col min="6" max="6" width="42" style="12" customWidth="1"/>
+    <col min="7" max="7" width="11.7109375" style="12" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B1" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D1" s="7" t="s">
+      <c r="B1" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>28</v>
+      <c r="E1" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="E2" s="5" t="s">
+      <c r="C2" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="E2" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="5"/>
+      <c r="F2" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="G2" s="14"/>
     </row>
     <row r="3" spans="2:7" ht="173.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="3"/>
-      <c r="D3" s="5"/>
+      <c r="B3" s="16"/>
+      <c r="D3" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2171,58 +2177,58 @@
   <dimension ref="B1:G3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="2"/>
-    <col min="2" max="2" width="58.85546875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="54.85546875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="40.42578125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="43.28515625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="42" style="2" customWidth="1"/>
-    <col min="7" max="7" width="77.85546875" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="9.140625" style="12"/>
+    <col min="2" max="2" width="58.85546875" style="12" customWidth="1"/>
+    <col min="3" max="3" width="54.85546875" style="12" customWidth="1"/>
+    <col min="4" max="4" width="40.42578125" style="12" customWidth="1"/>
+    <col min="5" max="5" width="43.28515625" style="12" customWidth="1"/>
+    <col min="6" max="6" width="42" style="12" customWidth="1"/>
+    <col min="7" max="7" width="77.85546875" style="12" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B1" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D1" s="7" t="s">
+      <c r="B1" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>28</v>
+      <c r="E1" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E2" s="5" t="s">
+      <c r="B2" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="G2" s="5"/>
+      <c r="C2" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="G2" s="14"/>
     </row>
     <row r="3" spans="2:7" ht="173.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="3"/>
-      <c r="C3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>14</v>
+      <c r="B3" s="16"/>
+      <c r="C3" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -2236,54 +2242,54 @@
   <dimension ref="B1:G3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="2"/>
-    <col min="2" max="2" width="58.85546875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="54.85546875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="40.42578125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="43.28515625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="42" style="2" customWidth="1"/>
-    <col min="7" max="7" width="77.85546875" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="9.140625" style="12"/>
+    <col min="2" max="2" width="58.85546875" style="12" customWidth="1"/>
+    <col min="3" max="3" width="54.85546875" style="12" customWidth="1"/>
+    <col min="4" max="4" width="40.42578125" style="12" customWidth="1"/>
+    <col min="5" max="5" width="43.28515625" style="12" customWidth="1"/>
+    <col min="6" max="6" width="42" style="12" customWidth="1"/>
+    <col min="7" max="7" width="77.85546875" style="12" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B1" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D1" s="7" t="s">
+      <c r="B1" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>28</v>
+      <c r="E1" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="G2" s="5"/>
+      <c r="B2" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="G2" s="14"/>
     </row>
     <row r="3" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="3"/>
-      <c r="D3" s="5"/>
+      <c r="B3" s="16"/>
+      <c r="D3" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2295,57 +2301,57 @@
   <dimension ref="B1:G3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="2"/>
-    <col min="2" max="2" width="58.85546875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="54.85546875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="40.42578125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="43.28515625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="42" style="2" customWidth="1"/>
-    <col min="7" max="7" width="77.85546875" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="9.140625" style="12"/>
+    <col min="2" max="2" width="58.85546875" style="12" customWidth="1"/>
+    <col min="3" max="3" width="54.85546875" style="12" customWidth="1"/>
+    <col min="4" max="4" width="40.42578125" style="12" customWidth="1"/>
+    <col min="5" max="5" width="43.28515625" style="12" customWidth="1"/>
+    <col min="6" max="6" width="42" style="12" customWidth="1"/>
+    <col min="7" max="7" width="77.85546875" style="12" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B1" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D1" s="7" t="s">
+      <c r="B1" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>28</v>
+      <c r="E1" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="G2" s="5"/>
+      <c r="C2" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="G2" s="14"/>
     </row>
     <row r="3" spans="2:7" ht="173.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="3"/>
-      <c r="C3" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D3" s="5"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="D3" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2360,62 +2366,62 @@
   <dimension ref="B1:G36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="2"/>
-    <col min="2" max="2" width="58.85546875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="54.85546875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="40.42578125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="43.28515625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="42" style="2" customWidth="1"/>
-    <col min="7" max="7" width="77.85546875" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="9.140625" style="12"/>
+    <col min="2" max="2" width="58.85546875" style="12" customWidth="1"/>
+    <col min="3" max="3" width="54.85546875" style="12" customWidth="1"/>
+    <col min="4" max="4" width="40.42578125" style="12" customWidth="1"/>
+    <col min="5" max="5" width="43.28515625" style="12" customWidth="1"/>
+    <col min="6" max="6" width="42" style="12" customWidth="1"/>
+    <col min="7" max="7" width="77.85546875" style="12" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B1" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D1" s="7" t="s">
+      <c r="B1" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>28</v>
+      <c r="E1" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="G2" s="5"/>
+      <c r="B2" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="G2" s="14"/>
     </row>
     <row r="3" spans="2:7" ht="173.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="3"/>
-      <c r="C3" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>62</v>
+      <c r="B3" s="16"/>
+      <c r="C3" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="36" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D36" s="14"/>
+      <c r="D36" s="20"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2427,57 +2433,57 @@
   <dimension ref="B1:G3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="2"/>
-    <col min="2" max="2" width="58.85546875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="54.85546875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="40.42578125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="43.28515625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="42" style="2" customWidth="1"/>
-    <col min="7" max="7" width="77.85546875" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="9.140625" style="12"/>
+    <col min="2" max="2" width="58.85546875" style="12" customWidth="1"/>
+    <col min="3" max="3" width="54.85546875" style="12" customWidth="1"/>
+    <col min="4" max="4" width="40.42578125" style="12" customWidth="1"/>
+    <col min="5" max="5" width="43.28515625" style="12" customWidth="1"/>
+    <col min="6" max="6" width="42" style="12" customWidth="1"/>
+    <col min="7" max="7" width="77.85546875" style="12" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B1" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D1" s="7" t="s">
+      <c r="B1" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>28</v>
+      <c r="E1" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="G2" s="5"/>
+      <c r="B2" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="G2" s="14"/>
     </row>
     <row r="3" spans="2:7" ht="173.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="3"/>
-      <c r="C3" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="D3" s="5"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="D3" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2492,57 +2498,57 @@
   <dimension ref="B1:G3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="2"/>
-    <col min="2" max="2" width="58.85546875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="54.85546875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="40.42578125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="43.28515625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="42" style="2" customWidth="1"/>
-    <col min="7" max="7" width="77.85546875" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="9.140625" style="12"/>
+    <col min="2" max="2" width="58.85546875" style="12" customWidth="1"/>
+    <col min="3" max="3" width="54.85546875" style="12" customWidth="1"/>
+    <col min="4" max="4" width="40.42578125" style="12" customWidth="1"/>
+    <col min="5" max="5" width="43.28515625" style="12" customWidth="1"/>
+    <col min="6" max="6" width="42" style="12" customWidth="1"/>
+    <col min="7" max="7" width="77.85546875" style="12" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B1" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D1" s="7" t="s">
+      <c r="B1" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>28</v>
+      <c r="E1" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="D2" s="5" t="s">
+      <c r="B2" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="G2" s="14"/>
+    </row>
+    <row r="3" spans="2:7" ht="173.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="16"/>
+      <c r="C3" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="E2" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="G2" s="5"/>
-    </row>
-    <row r="3" spans="2:7" ht="173.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="3"/>
-      <c r="C3" s="12" t="s">
-        <v>125</v>
-      </c>
-      <c r="D3" s="5"/>
+      <c r="D3" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2554,57 +2560,57 @@
   <dimension ref="B1:G3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="2"/>
-    <col min="2" max="2" width="58.85546875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="54.85546875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="40.42578125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="43.28515625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="42" style="2" customWidth="1"/>
-    <col min="7" max="7" width="77.85546875" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="9.140625" style="12"/>
+    <col min="2" max="2" width="58.85546875" style="12" customWidth="1"/>
+    <col min="3" max="3" width="54.85546875" style="12" customWidth="1"/>
+    <col min="4" max="4" width="40.42578125" style="12" customWidth="1"/>
+    <col min="5" max="5" width="43.28515625" style="12" customWidth="1"/>
+    <col min="6" max="6" width="42" style="12" customWidth="1"/>
+    <col min="7" max="7" width="77.85546875" style="12" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B1" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D1" s="7" t="s">
+      <c r="B1" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>28</v>
+      <c r="E1" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="G2" s="5"/>
+      <c r="B2" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>159</v>
+      </c>
+      <c r="G2" s="14"/>
     </row>
     <row r="3" spans="2:7" ht="173.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="3"/>
-      <c r="C3" s="12" t="s">
-        <v>127</v>
-      </c>
-      <c r="D3" s="5"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="D3" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2616,57 +2622,55 @@
   <dimension ref="B1:G3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="2"/>
-    <col min="2" max="2" width="58.85546875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="54.85546875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="40.42578125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="43.28515625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="42" style="2" customWidth="1"/>
-    <col min="7" max="7" width="77.85546875" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="9.140625" style="12"/>
+    <col min="2" max="2" width="58.85546875" style="12" customWidth="1"/>
+    <col min="3" max="3" width="54.85546875" style="12" customWidth="1"/>
+    <col min="4" max="4" width="40.42578125" style="12" customWidth="1"/>
+    <col min="5" max="5" width="43.28515625" style="12" customWidth="1"/>
+    <col min="6" max="6" width="42" style="12" customWidth="1"/>
+    <col min="7" max="7" width="77.85546875" style="12" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B1" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D1" s="7" t="s">
+      <c r="B1" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>28</v>
+      <c r="E1" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="G2" s="5"/>
+      <c r="B2" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>162</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="G2" s="14"/>
     </row>
     <row r="3" spans="2:7" ht="173.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="3"/>
-      <c r="C3" s="12" t="s">
-        <v>127</v>
-      </c>
-      <c r="D3" s="5"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2681,56 +2685,56 @@
   <dimension ref="B1:G3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="2"/>
-    <col min="2" max="2" width="58.85546875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="54.85546875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="40.42578125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="43.28515625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="42" style="2" customWidth="1"/>
-    <col min="7" max="7" width="77.85546875" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="9.140625" style="12"/>
+    <col min="2" max="2" width="58.85546875" style="12" customWidth="1"/>
+    <col min="3" max="3" width="54.85546875" style="12" customWidth="1"/>
+    <col min="4" max="4" width="40.42578125" style="12" customWidth="1"/>
+    <col min="5" max="5" width="43.28515625" style="12" customWidth="1"/>
+    <col min="6" max="6" width="42" style="12" customWidth="1"/>
+    <col min="7" max="7" width="77.85546875" style="12" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B1" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D1" s="7" t="s">
+      <c r="B1" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>28</v>
+      <c r="E1" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="D2" s="5" t="s">
+      <c r="C2" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="D2" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="14" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="3" spans="2:7" ht="173.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="3"/>
-      <c r="D3" s="5" t="s">
+      <c r="B3" s="16"/>
+      <c r="D3" s="14" t="s">
         <v>6</v>
       </c>
     </row>
@@ -2744,57 +2748,55 @@
   <dimension ref="B1:G3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="2"/>
-    <col min="2" max="2" width="58.85546875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="54.85546875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="40.42578125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="43.28515625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="42" style="2" customWidth="1"/>
-    <col min="7" max="7" width="77.85546875" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="9.140625" style="12"/>
+    <col min="2" max="2" width="58.85546875" style="12" customWidth="1"/>
+    <col min="3" max="3" width="54.85546875" style="12" customWidth="1"/>
+    <col min="4" max="4" width="40.42578125" style="12" customWidth="1"/>
+    <col min="5" max="5" width="43.28515625" style="12" customWidth="1"/>
+    <col min="6" max="6" width="42" style="12" customWidth="1"/>
+    <col min="7" max="7" width="27.28515625" style="12" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B1" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D1" s="7" t="s">
+      <c r="B1" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>28</v>
+      <c r="E1" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="G2" s="5"/>
+      <c r="B2" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>164</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="G2" s="14"/>
     </row>
     <row r="3" spans="2:7" ht="173.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="3"/>
-      <c r="C3" s="12" t="s">
-        <v>131</v>
-      </c>
-      <c r="D3" s="5"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2807,57 +2809,57 @@
   <dimension ref="B1:G3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="2"/>
-    <col min="2" max="2" width="58.85546875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="54.85546875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="40.42578125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="43.28515625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="42" style="2" customWidth="1"/>
-    <col min="7" max="7" width="77.85546875" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="9.140625" style="12"/>
+    <col min="2" max="2" width="58.85546875" style="12" customWidth="1"/>
+    <col min="3" max="3" width="54.85546875" style="12" customWidth="1"/>
+    <col min="4" max="4" width="40.42578125" style="12" customWidth="1"/>
+    <col min="5" max="5" width="43.28515625" style="12" customWidth="1"/>
+    <col min="6" max="6" width="42" style="12" customWidth="1"/>
+    <col min="7" max="7" width="11.28515625" style="12" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B1" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D1" s="7" t="s">
+      <c r="B1" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>28</v>
+      <c r="E1" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="G2" s="5"/>
+      <c r="C2" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>165</v>
+      </c>
+      <c r="G2" s="14"/>
     </row>
     <row r="3" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="3"/>
-      <c r="C3" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="D3" s="5"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="D3" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2870,57 +2872,57 @@
   <dimension ref="B1:G3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="2"/>
-    <col min="2" max="2" width="58.85546875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="54.85546875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="40.42578125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="43.28515625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="42" style="2" customWidth="1"/>
-    <col min="7" max="7" width="77.85546875" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="9.140625" style="12"/>
+    <col min="2" max="2" width="58.85546875" style="12" customWidth="1"/>
+    <col min="3" max="3" width="54.85546875" style="12" customWidth="1"/>
+    <col min="4" max="4" width="40.42578125" style="12" customWidth="1"/>
+    <col min="5" max="5" width="43.28515625" style="12" customWidth="1"/>
+    <col min="6" max="6" width="42" style="12" customWidth="1"/>
+    <col min="7" max="7" width="77.85546875" style="12" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B1" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D1" s="7" t="s">
+      <c r="B1" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>28</v>
+      <c r="E1" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="G2" s="5"/>
+      <c r="B2" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>168</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="G2" s="14"/>
     </row>
     <row r="3" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="3"/>
-      <c r="C3" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="D3" s="5"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="D3" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2932,57 +2934,57 @@
   <dimension ref="B1:G3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="2"/>
-    <col min="2" max="2" width="58.85546875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="54.85546875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="40.42578125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="43.28515625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="42" style="2" customWidth="1"/>
-    <col min="7" max="7" width="77.85546875" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="9.140625" style="12"/>
+    <col min="2" max="2" width="58.85546875" style="12" customWidth="1"/>
+    <col min="3" max="3" width="54.85546875" style="12" customWidth="1"/>
+    <col min="4" max="4" width="40.42578125" style="12" customWidth="1"/>
+    <col min="5" max="5" width="43.28515625" style="12" customWidth="1"/>
+    <col min="6" max="6" width="42" style="12" customWidth="1"/>
+    <col min="7" max="7" width="77.85546875" style="12" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B1" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D1" s="7" t="s">
+      <c r="B1" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>28</v>
+      <c r="E1" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="G2" s="5"/>
+      <c r="B2" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="G2" s="14"/>
     </row>
     <row r="3" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="3"/>
-      <c r="C3" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="D3" s="5"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="D3" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2994,57 +2996,57 @@
   <dimension ref="B1:G3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="2"/>
-    <col min="2" max="2" width="58.85546875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="54.85546875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="40.42578125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="43.28515625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="42" style="2" customWidth="1"/>
-    <col min="7" max="7" width="77.85546875" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="9.140625" style="12"/>
+    <col min="2" max="2" width="58.85546875" style="12" customWidth="1"/>
+    <col min="3" max="3" width="54.85546875" style="12" customWidth="1"/>
+    <col min="4" max="4" width="40.42578125" style="12" customWidth="1"/>
+    <col min="5" max="5" width="43.28515625" style="12" customWidth="1"/>
+    <col min="6" max="6" width="42" style="12" customWidth="1"/>
+    <col min="7" max="7" width="77.85546875" style="12" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B1" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D1" s="7" t="s">
+      <c r="B1" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>28</v>
+      <c r="E1" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="G2" s="5"/>
+      <c r="B2" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="G2" s="14"/>
     </row>
     <row r="3" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="3"/>
-      <c r="C3" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="D3" s="5"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="D3" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3056,57 +3058,57 @@
   <dimension ref="B1:G3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="2"/>
-    <col min="2" max="2" width="58.85546875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="54.85546875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="40.42578125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="43.28515625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="42" style="2" customWidth="1"/>
-    <col min="7" max="7" width="77.85546875" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="9.140625" style="12"/>
+    <col min="2" max="2" width="58.85546875" style="12" customWidth="1"/>
+    <col min="3" max="3" width="54.85546875" style="12" customWidth="1"/>
+    <col min="4" max="4" width="40.42578125" style="12" customWidth="1"/>
+    <col min="5" max="5" width="43.28515625" style="12" customWidth="1"/>
+    <col min="6" max="6" width="42" style="12" customWidth="1"/>
+    <col min="7" max="7" width="77.85546875" style="12" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B1" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D1" s="7" t="s">
+      <c r="B1" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>28</v>
+      <c r="E1" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="G2" s="5"/>
+      <c r="B2" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>174</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="G2" s="14"/>
     </row>
     <row r="3" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="3"/>
-      <c r="C3" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="D3" s="5"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="D3" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3118,57 +3120,57 @@
   <dimension ref="B1:G3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="2"/>
-    <col min="2" max="2" width="58.85546875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="54.85546875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="40.42578125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="43.28515625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="42" style="2" customWidth="1"/>
-    <col min="7" max="7" width="77.85546875" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="9.140625" style="12"/>
+    <col min="2" max="2" width="58.85546875" style="12" customWidth="1"/>
+    <col min="3" max="3" width="54.85546875" style="12" customWidth="1"/>
+    <col min="4" max="4" width="40.42578125" style="12" customWidth="1"/>
+    <col min="5" max="5" width="43.28515625" style="12" customWidth="1"/>
+    <col min="6" max="6" width="42" style="12" customWidth="1"/>
+    <col min="7" max="7" width="77.85546875" style="12" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B1" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D1" s="7" t="s">
+      <c r="B1" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>28</v>
+      <c r="E1" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="G2" s="5"/>
+      <c r="B2" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="G2" s="14"/>
     </row>
     <row r="3" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="3"/>
-      <c r="C3" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="D3" s="5"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="D3" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3183,57 +3185,57 @@
   <dimension ref="B1:G3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="2"/>
-    <col min="2" max="2" width="58.85546875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="54.85546875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="40.42578125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="43.28515625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="42" style="2" customWidth="1"/>
-    <col min="7" max="7" width="77.85546875" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="9.140625" style="12"/>
+    <col min="2" max="2" width="58.85546875" style="12" customWidth="1"/>
+    <col min="3" max="3" width="54.85546875" style="12" customWidth="1"/>
+    <col min="4" max="4" width="40.42578125" style="12" customWidth="1"/>
+    <col min="5" max="5" width="43.28515625" style="12" customWidth="1"/>
+    <col min="6" max="6" width="42" style="12" customWidth="1"/>
+    <col min="7" max="7" width="77.85546875" style="12" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="F2" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="G2" s="5"/>
+      <c r="G2" s="14"/>
     </row>
     <row r="3" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="3"/>
-      <c r="C3" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="D3" s="5"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="D3" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3245,57 +3247,57 @@
   <dimension ref="B1:G3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="2"/>
-    <col min="2" max="2" width="58.85546875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="54.85546875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="40.42578125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="43.28515625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="42" style="2" customWidth="1"/>
-    <col min="7" max="7" width="77.85546875" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="9.140625" style="12"/>
+    <col min="2" max="2" width="58.85546875" style="12" customWidth="1"/>
+    <col min="3" max="3" width="54.85546875" style="12" customWidth="1"/>
+    <col min="4" max="4" width="40.42578125" style="12" customWidth="1"/>
+    <col min="5" max="5" width="43.28515625" style="12" customWidth="1"/>
+    <col min="6" max="6" width="42" style="12" customWidth="1"/>
+    <col min="7" max="7" width="77.85546875" style="12" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B1" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D1" s="7" t="s">
+      <c r="B1" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>28</v>
+      <c r="E1" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="G2" s="5"/>
+      <c r="B2" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="G2" s="14"/>
     </row>
     <row r="3" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="3"/>
-      <c r="C3" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="D3" s="5"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="D3" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3310,57 +3312,57 @@
   <dimension ref="B1:G3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="2"/>
-    <col min="2" max="2" width="58.85546875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="54.85546875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="40.42578125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="43.28515625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="42" style="2" customWidth="1"/>
-    <col min="7" max="7" width="77.85546875" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="9.140625" style="12"/>
+    <col min="2" max="2" width="58.85546875" style="12" customWidth="1"/>
+    <col min="3" max="3" width="54.85546875" style="12" customWidth="1"/>
+    <col min="4" max="4" width="40.42578125" style="12" customWidth="1"/>
+    <col min="5" max="5" width="43.28515625" style="12" customWidth="1"/>
+    <col min="6" max="6" width="42" style="12" customWidth="1"/>
+    <col min="7" max="7" width="77.85546875" style="12" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B1" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D1" s="7" t="s">
+      <c r="B1" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>28</v>
+      <c r="E1" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="G2" s="5"/>
+      <c r="B2" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="G2" s="14"/>
     </row>
     <row r="3" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="3"/>
-      <c r="C3" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="D3" s="5"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="D3" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3372,56 +3374,55 @@
   <dimension ref="B1:G3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="2"/>
-    <col min="2" max="2" width="58.85546875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="54.85546875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="40.42578125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="43.28515625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="42" style="2" customWidth="1"/>
-    <col min="7" max="7" width="77.85546875" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="9.140625" style="12"/>
+    <col min="2" max="2" width="58.85546875" style="12" customWidth="1"/>
+    <col min="3" max="3" width="54.85546875" style="12" customWidth="1"/>
+    <col min="4" max="4" width="40.42578125" style="12" customWidth="1"/>
+    <col min="5" max="5" width="43.28515625" style="12" customWidth="1"/>
+    <col min="6" max="6" width="42" style="12" customWidth="1"/>
+    <col min="7" max="7" width="77.85546875" style="12" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B1" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="B1" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="G2" s="14"/>
+    </row>
+    <row r="3" spans="2:7" ht="173.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="16"/>
+      <c r="D3" s="14" t="s">
         <v>26</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="G2" s="5"/>
-    </row>
-    <row r="3" spans="2:7" ht="173.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="3"/>
-      <c r="C3"/>
-      <c r="D3" s="5" t="s">
-        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -3434,57 +3435,57 @@
   <dimension ref="B1:G3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="2"/>
-    <col min="2" max="2" width="58.85546875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="54.85546875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="40.42578125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="43.28515625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="42" style="2" customWidth="1"/>
-    <col min="7" max="7" width="77.85546875" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="9.140625" style="12"/>
+    <col min="2" max="2" width="58.85546875" style="12" customWidth="1"/>
+    <col min="3" max="3" width="54.85546875" style="12" customWidth="1"/>
+    <col min="4" max="4" width="40.42578125" style="12" customWidth="1"/>
+    <col min="5" max="5" width="43.28515625" style="12" customWidth="1"/>
+    <col min="6" max="6" width="42" style="12" customWidth="1"/>
+    <col min="7" max="7" width="77.85546875" style="12" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B1" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D1" s="7" t="s">
+      <c r="B1" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>28</v>
+      <c r="E1" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="G2" s="5"/>
+      <c r="B2" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>179</v>
+      </c>
+      <c r="G2" s="14"/>
     </row>
     <row r="3" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="3"/>
-      <c r="C3" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="D3" s="5"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="D3" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3499,57 +3500,57 @@
   <dimension ref="B1:G3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="2"/>
-    <col min="2" max="2" width="58.85546875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="54.85546875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="40.42578125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="43.28515625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="42" style="2" customWidth="1"/>
-    <col min="7" max="7" width="77.85546875" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="9.140625" style="12"/>
+    <col min="2" max="2" width="58.85546875" style="12" customWidth="1"/>
+    <col min="3" max="3" width="54.85546875" style="12" customWidth="1"/>
+    <col min="4" max="4" width="40.42578125" style="12" customWidth="1"/>
+    <col min="5" max="5" width="43.28515625" style="12" customWidth="1"/>
+    <col min="6" max="6" width="42" style="12" customWidth="1"/>
+    <col min="7" max="7" width="77.85546875" style="12" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B1" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D1" s="7" t="s">
+      <c r="B1" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>28</v>
+      <c r="E1" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>142</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="G2" s="5"/>
+      <c r="B2" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="G2" s="14"/>
     </row>
     <row r="3" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="3"/>
-      <c r="C3" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="D3" s="5"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="D3" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3561,53 +3562,53 @@
   <dimension ref="B1:G3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="2"/>
-    <col min="2" max="2" width="58.85546875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="54.85546875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="40.42578125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="43.28515625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="42" style="2" customWidth="1"/>
-    <col min="7" max="7" width="77.85546875" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="9.140625" style="12"/>
+    <col min="2" max="2" width="58.85546875" style="12" customWidth="1"/>
+    <col min="3" max="3" width="54.85546875" style="12" customWidth="1"/>
+    <col min="4" max="4" width="40.42578125" style="12" customWidth="1"/>
+    <col min="5" max="5" width="43.28515625" style="12" customWidth="1"/>
+    <col min="6" max="6" width="42" style="12" customWidth="1"/>
+    <col min="7" max="7" width="77.85546875" style="12" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B1" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D1" s="7" t="s">
+      <c r="B1" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>28</v>
+      <c r="E1" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
+      <c r="B2" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
     </row>
     <row r="3" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="3"/>
-      <c r="C3" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="D3" s="5"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="D3" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3619,53 +3620,53 @@
   <dimension ref="B1:G3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="2"/>
-    <col min="2" max="2" width="58.85546875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="54.85546875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="40.42578125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="43.28515625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="42" style="2" customWidth="1"/>
-    <col min="7" max="7" width="77.85546875" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="9.140625" style="12"/>
+    <col min="2" max="2" width="58.85546875" style="12" customWidth="1"/>
+    <col min="3" max="3" width="54.85546875" style="12" customWidth="1"/>
+    <col min="4" max="4" width="40.42578125" style="12" customWidth="1"/>
+    <col min="5" max="5" width="43.28515625" style="12" customWidth="1"/>
+    <col min="6" max="6" width="42" style="12" customWidth="1"/>
+    <col min="7" max="7" width="77.85546875" style="12" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B1" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D1" s="7" t="s">
+      <c r="B1" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>28</v>
+      <c r="E1" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>156</v>
-      </c>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
+      <c r="B2" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
     </row>
     <row r="3" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="3"/>
-      <c r="C3" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="D3" s="5"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="D3" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3677,53 +3678,53 @@
   <dimension ref="B1:G3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="2"/>
-    <col min="2" max="2" width="58.85546875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="54.85546875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="40.42578125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="43.28515625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="42" style="2" customWidth="1"/>
-    <col min="7" max="7" width="77.85546875" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="9.140625" style="12"/>
+    <col min="2" max="2" width="58.85546875" style="12" customWidth="1"/>
+    <col min="3" max="3" width="54.85546875" style="12" customWidth="1"/>
+    <col min="4" max="4" width="40.42578125" style="12" customWidth="1"/>
+    <col min="5" max="5" width="43.28515625" style="12" customWidth="1"/>
+    <col min="6" max="6" width="42" style="12" customWidth="1"/>
+    <col min="7" max="7" width="77.85546875" style="12" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B1" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D1" s="7" t="s">
+      <c r="B1" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>28</v>
+      <c r="E1" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>158</v>
-      </c>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
+      <c r="B2" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
     </row>
     <row r="3" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="3"/>
-      <c r="C3" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="D3" s="5"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="D3" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3735,53 +3736,53 @@
   <dimension ref="B1:G3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="2"/>
-    <col min="2" max="2" width="58.85546875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="54.85546875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="40.42578125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="43.28515625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="42" style="2" customWidth="1"/>
-    <col min="7" max="7" width="77.85546875" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="9.140625" style="12"/>
+    <col min="2" max="2" width="58.85546875" style="12" customWidth="1"/>
+    <col min="3" max="3" width="54.85546875" style="12" customWidth="1"/>
+    <col min="4" max="4" width="40.42578125" style="12" customWidth="1"/>
+    <col min="5" max="5" width="43.28515625" style="12" customWidth="1"/>
+    <col min="6" max="6" width="42" style="12" customWidth="1"/>
+    <col min="7" max="7" width="77.85546875" style="12" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B1" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D1" s="7" t="s">
+      <c r="B1" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>28</v>
+      <c r="E1" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
+      <c r="B2" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
     </row>
     <row r="3" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="3"/>
-      <c r="C3" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="D3" s="5"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="D3" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3793,53 +3794,53 @@
   <dimension ref="B1:G3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="2"/>
-    <col min="2" max="2" width="58.85546875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="54.85546875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="40.42578125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="43.28515625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="42" style="2" customWidth="1"/>
-    <col min="7" max="7" width="77.85546875" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="9.140625" style="12"/>
+    <col min="2" max="2" width="58.85546875" style="12" customWidth="1"/>
+    <col min="3" max="3" width="54.85546875" style="12" customWidth="1"/>
+    <col min="4" max="4" width="40.42578125" style="12" customWidth="1"/>
+    <col min="5" max="5" width="43.28515625" style="12" customWidth="1"/>
+    <col min="6" max="6" width="42" style="12" customWidth="1"/>
+    <col min="7" max="7" width="77.85546875" style="12" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B1" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D1" s="7" t="s">
+      <c r="B1" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>28</v>
+      <c r="E1" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
+      <c r="B2" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
     </row>
     <row r="3" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="3"/>
-      <c r="C3" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="D3" s="5"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="D3" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3854,57 +3855,57 @@
   <dimension ref="B1:G3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="2"/>
-    <col min="2" max="2" width="58.85546875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="54.85546875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="40.42578125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="43.28515625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="42" style="2" customWidth="1"/>
-    <col min="7" max="7" width="77.85546875" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="9.140625" style="12"/>
+    <col min="2" max="2" width="58.85546875" style="12" customWidth="1"/>
+    <col min="3" max="3" width="54.85546875" style="12" customWidth="1"/>
+    <col min="4" max="4" width="40.42578125" style="12" customWidth="1"/>
+    <col min="5" max="5" width="43.28515625" style="12" customWidth="1"/>
+    <col min="6" max="6" width="42" style="12" customWidth="1"/>
+    <col min="7" max="7" width="77.85546875" style="12" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B1" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D1" s="7" t="s">
+      <c r="B1" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>28</v>
+      <c r="E1" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="G2" s="5"/>
+      <c r="B2" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="G2" s="14"/>
     </row>
     <row r="3" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="3"/>
-      <c r="C3" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="D3" s="5"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="D3" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3916,53 +3917,53 @@
   <dimension ref="B1:G3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="2"/>
-    <col min="2" max="2" width="58.85546875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="54.85546875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="40.42578125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="43.28515625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="42" style="2" customWidth="1"/>
-    <col min="7" max="7" width="77.85546875" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="9.140625" style="12"/>
+    <col min="2" max="2" width="58.85546875" style="12" customWidth="1"/>
+    <col min="3" max="3" width="54.85546875" style="12" customWidth="1"/>
+    <col min="4" max="4" width="40.42578125" style="12" customWidth="1"/>
+    <col min="5" max="5" width="43.28515625" style="12" customWidth="1"/>
+    <col min="6" max="6" width="42" style="12" customWidth="1"/>
+    <col min="7" max="7" width="77.85546875" style="12" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B1" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D1" s="7" t="s">
+      <c r="B1" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>28</v>
+      <c r="E1" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>147</v>
-      </c>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
+      <c r="B2" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
     </row>
     <row r="3" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="3"/>
-      <c r="C3" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="D3" s="5"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="D3" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3974,53 +3975,53 @@
   <dimension ref="B1:G3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="2"/>
-    <col min="2" max="2" width="58.85546875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="54.85546875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="40.42578125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="43.28515625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="42" style="2" customWidth="1"/>
-    <col min="7" max="7" width="77.85546875" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="9.140625" style="12"/>
+    <col min="2" max="2" width="58.85546875" style="12" customWidth="1"/>
+    <col min="3" max="3" width="54.85546875" style="12" customWidth="1"/>
+    <col min="4" max="4" width="40.42578125" style="12" customWidth="1"/>
+    <col min="5" max="5" width="43.28515625" style="12" customWidth="1"/>
+    <col min="6" max="6" width="42" style="12" customWidth="1"/>
+    <col min="7" max="7" width="77.85546875" style="12" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B1" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D1" s="7" t="s">
+      <c r="B1" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>28</v>
+      <c r="E1" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
+      <c r="B2" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
     </row>
     <row r="3" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="3"/>
-      <c r="C3" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="D3" s="5"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="D3" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4032,55 +4033,54 @@
   <dimension ref="B1:G3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="2"/>
-    <col min="2" max="2" width="58.85546875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="54.85546875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="40.42578125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="43.28515625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="42" style="2" customWidth="1"/>
-    <col min="7" max="7" width="77.85546875" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="9.140625" style="12"/>
+    <col min="2" max="2" width="58.85546875" style="12" customWidth="1"/>
+    <col min="3" max="3" width="54.85546875" style="12" customWidth="1"/>
+    <col min="4" max="4" width="40.42578125" style="12" customWidth="1"/>
+    <col min="5" max="5" width="43.28515625" style="12" customWidth="1"/>
+    <col min="6" max="6" width="42" style="12" customWidth="1"/>
+    <col min="7" max="7" width="77.85546875" style="12" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B1" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D1" s="7" t="s">
+      <c r="B1" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>28</v>
+      <c r="E1" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="G2" s="5"/>
+      <c r="B2" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="G2" s="14"/>
     </row>
     <row r="3" spans="2:7" ht="173.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="3"/>
-      <c r="C3"/>
-      <c r="D3" s="5" t="s">
+      <c r="B3" s="16"/>
+      <c r="D3" s="14" t="s">
         <v>2</v>
       </c>
     </row>
@@ -4094,53 +4094,53 @@
   <dimension ref="B1:G3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="2"/>
-    <col min="2" max="2" width="58.85546875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="54.85546875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="40.42578125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="43.28515625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="42" style="2" customWidth="1"/>
-    <col min="7" max="7" width="77.85546875" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="9.140625" style="12"/>
+    <col min="2" max="2" width="58.85546875" style="12" customWidth="1"/>
+    <col min="3" max="3" width="54.85546875" style="12" customWidth="1"/>
+    <col min="4" max="4" width="40.42578125" style="12" customWidth="1"/>
+    <col min="5" max="5" width="43.28515625" style="12" customWidth="1"/>
+    <col min="6" max="6" width="42" style="12" customWidth="1"/>
+    <col min="7" max="7" width="77.85546875" style="12" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B1" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D1" s="7" t="s">
+      <c r="B1" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>28</v>
+      <c r="E1" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
+      <c r="B2" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
     </row>
     <row r="3" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="3"/>
-      <c r="C3" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="D3" s="5"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="D3" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4165,29 +4165,29 @@
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="1" t="s">
-        <v>119</v>
+        <v>90</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D1" s="7" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="6"/>
       <c r="C2" s="5"/>
       <c r="D2" s="5" t="s">
-        <v>76</v>
+        <v>56</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
@@ -4206,57 +4206,57 @@
   <dimension ref="B1:G3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="2"/>
-    <col min="2" max="2" width="58.85546875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="54.85546875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="40.42578125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="43.28515625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="42" style="2" customWidth="1"/>
-    <col min="7" max="7" width="77.85546875" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="9.140625" style="12"/>
+    <col min="2" max="2" width="58.85546875" style="12" customWidth="1"/>
+    <col min="3" max="3" width="54.85546875" style="12" customWidth="1"/>
+    <col min="4" max="4" width="40.42578125" style="12" customWidth="1"/>
+    <col min="5" max="5" width="43.28515625" style="12" customWidth="1"/>
+    <col min="6" max="6" width="42" style="12" customWidth="1"/>
+    <col min="7" max="7" width="77.85546875" style="12" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B1" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D1" s="7" t="s">
+      <c r="B1" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="4" t="s">
+      <c r="E1" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="G2" s="14"/>
+    </row>
+    <row r="3" spans="2:7" ht="173.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="16"/>
+      <c r="C3" s="18" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="G2" s="5"/>
-    </row>
-    <row r="3" spans="2:7" ht="173.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="3"/>
-      <c r="C3" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="14" t="s">
         <v>2</v>
       </c>
     </row>
@@ -4270,57 +4270,57 @@
   <dimension ref="B1:G3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="2"/>
-    <col min="2" max="2" width="58.85546875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="54.85546875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="40.42578125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="43.28515625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="42" style="2" customWidth="1"/>
-    <col min="7" max="7" width="77.85546875" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="9.140625" style="12"/>
+    <col min="2" max="2" width="58.85546875" style="12" customWidth="1"/>
+    <col min="3" max="3" width="54.85546875" style="12" customWidth="1"/>
+    <col min="4" max="4" width="40.42578125" style="12" customWidth="1"/>
+    <col min="5" max="5" width="43.28515625" style="12" customWidth="1"/>
+    <col min="6" max="6" width="42" style="12" customWidth="1"/>
+    <col min="7" max="7" width="77.85546875" style="12" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B1" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D1" s="7" t="s">
+      <c r="B1" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="4" t="s">
+      <c r="E1" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="G2" s="14"/>
+    </row>
+    <row r="3" spans="2:7" ht="173.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="16"/>
+      <c r="C3" s="18" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="G2" s="5"/>
-    </row>
-    <row r="3" spans="2:7" ht="173.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="3"/>
-      <c r="C3" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="D3" s="5"/>
+      <c r="D3" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4332,63 +4332,63 @@
   <dimension ref="B1:G4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="2"/>
-    <col min="2" max="2" width="58.85546875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="54.85546875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="40.42578125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="43.28515625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="42" style="2" customWidth="1"/>
-    <col min="7" max="7" width="77.85546875" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="9.140625" style="12"/>
+    <col min="2" max="2" width="58.85546875" style="12" customWidth="1"/>
+    <col min="3" max="3" width="54.85546875" style="12" customWidth="1"/>
+    <col min="4" max="4" width="40.42578125" style="12" customWidth="1"/>
+    <col min="5" max="5" width="43.28515625" style="12" customWidth="1"/>
+    <col min="6" max="6" width="42" style="12" customWidth="1"/>
+    <col min="7" max="7" width="77.85546875" style="12" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B1" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D1" s="7" t="s">
+      <c r="B1" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="4" t="s">
+      <c r="E1" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>145</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="G2" s="14"/>
+    </row>
+    <row r="3" spans="2:7" ht="73.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="16"/>
+      <c r="C3" s="18" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="G2" s="5"/>
-    </row>
-    <row r="3" spans="2:7" ht="73.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="3"/>
-      <c r="C3" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>78</v>
+      <c r="D3" s="14" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="2:7" ht="285" x14ac:dyDescent="0.25">
-      <c r="D4" s="13" t="s">
-        <v>79</v>
+      <c r="D4" s="16" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -4402,55 +4402,55 @@
   <dimension ref="B1:G3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="2"/>
-    <col min="2" max="2" width="58.85546875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="54.85546875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="40.42578125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="43.28515625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="42" style="2" customWidth="1"/>
-    <col min="7" max="7" width="77.85546875" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="9.140625" style="12"/>
+    <col min="2" max="2" width="58.85546875" style="12" customWidth="1"/>
+    <col min="3" max="3" width="54.85546875" style="12" customWidth="1"/>
+    <col min="4" max="4" width="40.42578125" style="12" customWidth="1"/>
+    <col min="5" max="5" width="43.28515625" style="12" customWidth="1"/>
+    <col min="6" max="6" width="42" style="12" customWidth="1"/>
+    <col min="7" max="7" width="77.85546875" style="12" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B1" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D1" s="7" t="s">
+      <c r="B1" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>28</v>
+      <c r="E1" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="G2" s="5"/>
+      <c r="B2" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>144</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="G2" s="14"/>
     </row>
     <row r="3" spans="2:7" ht="173.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="3"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="5" t="s">
+      <c r="B3" s="16"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="14" t="s">
         <v>2</v>
       </c>
     </row>
@@ -4464,56 +4464,56 @@
   <dimension ref="B1:G3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="2"/>
-    <col min="2" max="2" width="58.85546875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="54.85546875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="40.42578125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="43.28515625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="42" style="2" customWidth="1"/>
-    <col min="7" max="7" width="77.85546875" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="9.140625" style="12"/>
+    <col min="2" max="2" width="58.85546875" style="12" customWidth="1"/>
+    <col min="3" max="3" width="54.85546875" style="12" customWidth="1"/>
+    <col min="4" max="4" width="40.42578125" style="12" customWidth="1"/>
+    <col min="5" max="5" width="43.28515625" style="12" customWidth="1"/>
+    <col min="6" max="6" width="42" style="12" customWidth="1"/>
+    <col min="7" max="7" width="77.85546875" style="12" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B1" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D1" s="7" t="s">
+      <c r="B1" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>28</v>
+      <c r="E1" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="G2" s="5"/>
+      <c r="B2" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="G2" s="14"/>
     </row>
     <row r="3" spans="2:7" ht="173.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="3"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="5" t="s">
-        <v>86</v>
+      <c r="B3" s="16"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="14" t="s">
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -4522,21 +4522,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F0D812EB0939BE44B372FF1F45A9F73C" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="b279ff35aeca1c14d8137b0da22afbf9">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="63d4114e-1bef-4718-838e-9be3cc0e7df4" xmlns:ns4="89118cec-cb09-49c5-a79b-3d4b3e9d9980" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2c90ea5fa4cf6378d877eb3f32d57d39" ns3:_="" ns4:_="">
     <xsd:import namespace="63d4114e-1bef-4718-838e-9be3cc0e7df4"/>
@@ -4733,32 +4718,22 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CEFB7BEA-F1DC-4002-BBA4-F3BBCE3A973D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="89118cec-cb09-49c5-a79b-3d4b3e9d9980"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="63d4114e-1bef-4718-838e-9be3cc0e7df4"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0A8ED665-E737-40E7-B55A-D5579DF920C2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{53F54199-27FD-4E4A-88C4-16904FF3AA53}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4775,4 +4750,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CEFB7BEA-F1DC-4002-BBA4-F3BBCE3A973D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="89118cec-cb09-49c5-a79b-3d4b3e9d9980"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="63d4114e-1bef-4718-838e-9be3cc0e7df4"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0A8ED665-E737-40E7-B55A-D5579DF920C2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>